--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="282">
   <si>
     <t>50001579- "XEMORTIZ C. MEXICANA"</t>
   </si>
@@ -106,52 +106,55 @@
     <t>francisca@zitron.com</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216774205554623</t>
+  </si>
+  <si>
+    <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t>1216774244989628</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
+  </si>
+  <si>
+    <t>1216774244989646</t>
+  </si>
+  <si>
+    <t>Definicion Tecnica de componentes principales</t>
+  </si>
+  <si>
+    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377,Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1216774094321288</t>
+  </si>
+  <si>
+    <t>Plazo Contractual</t>
+  </si>
+  <si>
+    <t>1216769310026487</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1216774225564664</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT 4377,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216774205554623</t>
-  </si>
-  <si>
-    <t>Apertura pedido</t>
-  </si>
-  <si>
-    <t>1216774244989628</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
-  </si>
-  <si>
-    <t>1216774244989646</t>
-  </si>
-  <si>
-    <t>Definicion Tecnica de componentes principales</t>
-  </si>
-  <si>
-    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377,Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1216774094321288</t>
-  </si>
-  <si>
-    <t>Plazo Contractual</t>
-  </si>
-  <si>
-    <t>1216769310026487</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1216774225564664</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT 4377,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -917,7 +920,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
@@ -927,7 +930,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
   </fills>
@@ -1531,7 +1534,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46225.58441605324</v>
+        <v>46226.202111631945</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1592,7 +1595,7 @@
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46225.58441657407</v>
+        <v>46226.2021175463</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1653,7 +1656,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46225.584417094906</v>
+        <v>46226.20211158565</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -1714,7 +1717,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46225.58441765046</v>
+        <v>46226.202111875</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -1775,7 +1778,7 @@
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46225.5844181713</v>
+        <v>46226.20211157408</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -1883,7 +1886,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46225.584550405096</v>
+        <v>46226.17318585648</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>44</v>
@@ -1927,19 +1930,19 @@
       <c r="R11" s="8">
         <v>46226</v>
       </c>
-      <c r="S11" s="10" t="s">
-        <v>31</v>
+      <c r="S11" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T11" s="9">
         <v>0</v>
       </c>
-      <c r="U11" s="12" t="s">
-        <v>47</v>
+      <c r="U11" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="5">
         <v>46225.0091897338</v>
@@ -1949,7 +1952,7 @@
         <v>46225.00945758102</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>25</v>
@@ -1973,7 +1976,7 @@
         <v>26</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>26</v>
@@ -1986,7 +1989,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="8">
         <v>46225.009357546296</v>
@@ -1996,16 +1999,16 @@
         <v>46225.01037886574</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="8">
         <v>46226</v>
@@ -2023,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q13" s="8">
         <v>46227</v>
@@ -2037,19 +2040,19 @@
       <c r="R13" s="8">
         <v>46226</v>
       </c>
-      <c r="S13" s="10" t="s">
-        <v>31</v>
+      <c r="S13" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T13" s="9">
         <v>0</v>
       </c>
-      <c r="U13" s="12" t="s">
-        <v>47</v>
+      <c r="U13" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="5">
         <v>46225.00936541667</v>
@@ -2059,16 +2062,16 @@
         <v>46225.01040789352</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I14" s="5">
         <v>46226</v>
@@ -2086,13 +2089,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="5">
         <v>46227</v>
@@ -2100,19 +2103,19 @@
       <c r="R14" s="5">
         <v>46226</v>
       </c>
-      <c r="S14" s="10" t="s">
-        <v>31</v>
+      <c r="S14" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="12" t="s">
-        <v>47</v>
+      <c r="U14" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="8">
         <v>46225.009373043984</v>
@@ -2122,16 +2125,16 @@
         <v>46225.01044820602</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I15" s="8">
         <v>46226</v>
@@ -2149,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q15" s="8">
         <v>46227</v>
@@ -2163,19 +2166,19 @@
       <c r="R15" s="8">
         <v>46226</v>
       </c>
-      <c r="S15" s="10" t="s">
-        <v>31</v>
+      <c r="S15" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T15" s="9">
         <v>0</v>
       </c>
-      <c r="U15" s="12" t="s">
-        <v>47</v>
+      <c r="U15" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5">
         <v>46225.00919548611</v>
@@ -2185,7 +2188,7 @@
         <v>46225.00945971065</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2209,7 +2212,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2222,7 +2225,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="8">
         <v>46225.00938174769</v>
@@ -2232,16 +2235,16 @@
         <v>46225.01046802083</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I17" s="8">
         <v>46245</v>
@@ -2259,13 +2262,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="8">
         <v>46246</v>
@@ -2273,19 +2276,19 @@
       <c r="R17" s="8">
         <v>46245</v>
       </c>
-      <c r="S17" s="10" t="s">
-        <v>31</v>
+      <c r="S17" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T17" s="9">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>47</v>
+      <c r="U17" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5">
         <v>46225.009388923616</v>
@@ -2295,16 +2298,16 @@
         <v>46225.010489479166</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I18" s="5">
         <v>46245</v>
@@ -2322,13 +2325,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2336,19 +2339,19 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="10" t="s">
-        <v>31</v>
+      <c r="S18" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>47</v>
+      <c r="U18" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="8">
         <v>46225.009394699075</v>
@@ -2358,16 +2361,16 @@
         <v>46225.010513518515</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I19" s="8">
         <v>46245</v>
@@ -2385,13 +2388,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="8">
         <v>46246</v>
@@ -2399,19 +2402,19 @@
       <c r="R19" s="8">
         <v>46245</v>
       </c>
-      <c r="S19" s="10" t="s">
-        <v>31</v>
+      <c r="S19" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T19" s="9">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>47</v>
+      <c r="U19" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5">
         <v>46225.00940033565</v>
@@ -2421,16 +2424,16 @@
         <v>46225.010537939816</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I20" s="5">
         <v>46245</v>
@@ -2448,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2462,19 +2465,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="10" t="s">
-        <v>31</v>
+      <c r="S20" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="12" t="s">
-        <v>47</v>
+      <c r="U20" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8">
         <v>46225.00920047454</v>
@@ -2484,7 +2487,7 @@
         <v>46225.00964425926</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2508,7 +2511,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2521,7 +2524,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>46225.00940686342</v>
@@ -2531,16 +2534,16 @@
         <v>46225.01056048612</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2558,13 +2561,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2572,19 +2575,19 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="10" t="s">
-        <v>31</v>
+      <c r="S22" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>47</v>
+      <c r="U22" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="8">
         <v>46225.00941383102</v>
@@ -2594,16 +2597,16 @@
         <v>46225.01069787037</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I23" s="8">
         <v>46247</v>
@@ -2621,29 +2624,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
-      <c r="S23" s="10" t="s">
-        <v>31</v>
+      <c r="S23" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>47</v>
+      <c r="U23" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5">
         <v>46225.00942686343</v>
@@ -2653,16 +2656,16 @@
         <v>46225.010714247685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2680,29 +2683,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="10" t="s">
-        <v>31</v>
+      <c r="S24" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>47</v>
+      <c r="U24" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="8">
         <v>46225.00943440972</v>
@@ -2712,16 +2715,16 @@
         <v>46225.01060155092</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I25" s="8">
         <v>46247</v>
@@ -2739,10 +2742,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2753,19 +2756,19 @@
       <c r="R25" s="8">
         <v>46247</v>
       </c>
-      <c r="S25" s="10" t="s">
-        <v>31</v>
+      <c r="S25" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>47</v>
+      <c r="U25" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="5">
         <v>46225.00944026621</v>
@@ -2775,16 +2778,16 @@
         <v>46225.010778923606</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -2802,13 +2805,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2818,7 +2821,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B27" s="8">
         <v>46225.0094466088</v>
@@ -2828,16 +2831,16 @@
         <v>46225.010798159725</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I27" s="8">
         <v>46251</v>
@@ -2855,13 +2858,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2871,7 +2874,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" s="5">
         <v>46225.00949415509</v>
@@ -2881,16 +2884,16 @@
         <v>46225.01062606482</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -2908,10 +2911,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -2922,19 +2925,19 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="10" t="s">
-        <v>31</v>
+      <c r="S28" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>47</v>
+      <c r="U28" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="8">
         <v>46225.00950069445</v>
@@ -2944,16 +2947,16 @@
         <v>46225.01085252315</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" s="8">
         <v>46247</v>
@@ -2971,13 +2974,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -2987,7 +2990,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" s="5">
         <v>46225.00950701389</v>
@@ -2997,16 +3000,16 @@
         <v>46225.01087347222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3024,13 +3027,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3040,7 +3043,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" s="8">
         <v>46225.009512488425</v>
@@ -3050,16 +3053,16 @@
         <v>46225.01064516204</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I31" s="8">
         <v>46247</v>
@@ -3077,10 +3080,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3091,19 +3094,19 @@
       <c r="R31" s="8">
         <v>46247</v>
       </c>
-      <c r="S31" s="10" t="s">
-        <v>31</v>
+      <c r="S31" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>47</v>
+      <c r="U31" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3113,16 +3116,16 @@
         <v>46225.01092217593</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3140,13 +3143,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3156,7 +3159,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="8">
         <v>46225.0095310301</v>
@@ -3166,16 +3169,16 @@
         <v>46225.010939224536</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I33" s="8">
         <v>46258</v>
@@ -3193,13 +3196,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3209,7 +3212,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3219,16 +3222,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3246,13 +3249,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3262,7 +3265,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="8">
         <v>46225.00954297454</v>
@@ -3272,7 +3275,7 @@
         <v>46225.00964719907</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>25</v>
@@ -3296,7 +3299,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3309,7 +3312,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
@@ -3319,16 +3322,16 @@
         <v>46225.01102203704</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3346,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>44</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3360,19 +3363,19 @@
       <c r="R36" s="5">
         <v>46230</v>
       </c>
-      <c r="S36" s="10" t="s">
-        <v>31</v>
+      <c r="S36" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>47</v>
+      <c r="U36" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B37" s="8">
         <v>46225.009553993055</v>
@@ -3382,16 +3385,16 @@
         <v>46225.01104386574</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46237</v>
@@ -3409,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q37" s="8">
         <v>46241</v>
@@ -3423,19 +3426,19 @@
       <c r="R37" s="8">
         <v>46237</v>
       </c>
-      <c r="S37" s="10" t="s">
-        <v>31</v>
+      <c r="S37" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
-        <v>47</v>
+      <c r="U37" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5">
         <v>46225.00956064815</v>
@@ -3445,16 +3448,16 @@
         <v>46225.01522170139</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3472,13 +3475,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3486,19 +3489,19 @@
       <c r="R38" s="5">
         <v>46244</v>
       </c>
-      <c r="S38" s="10" t="s">
-        <v>31</v>
+      <c r="S38" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
-        <v>47</v>
+      <c r="U38" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" s="8">
         <v>46225.00957443287</v>
@@ -3508,16 +3511,16 @@
         <v>46225.01576019676</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I39" s="8">
         <v>46290</v>
@@ -3535,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q39" s="8">
         <v>46290</v>
@@ -3549,19 +3552,19 @@
       <c r="R39" s="8">
         <v>46290</v>
       </c>
-      <c r="S39" s="10" t="s">
-        <v>31</v>
+      <c r="S39" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
-      <c r="U39" s="12" t="s">
-        <v>47</v>
+      <c r="U39" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3571,16 +3574,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3596,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3612,7 +3615,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" s="8">
         <v>46225.00958684028</v>
@@ -3622,16 +3625,16 @@
         <v>46225.01157688657</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="8">
@@ -3647,13 +3650,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3663,7 +3666,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3673,7 +3676,7 @@
         <v>46225.009844733795</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3697,7 +3700,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3710,7 +3713,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B43" s="8">
         <v>46225.00968099537</v>
@@ -3720,16 +3723,16 @@
         <v>46225.011108125</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3745,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q43" s="8">
         <v>46260</v>
@@ -3759,19 +3762,19 @@
       <c r="R43" s="8">
         <v>46260</v>
       </c>
-      <c r="S43" s="10" t="s">
-        <v>31</v>
+      <c r="S43" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>47</v>
+      <c r="U43" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
@@ -3781,16 +3784,16 @@
         <v>46225.01115158565</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3808,13 +3811,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3822,19 +3825,19 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="10" t="s">
-        <v>31</v>
+      <c r="S44" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>47</v>
+      <c r="U44" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" s="8">
         <v>46225.00969839121</v>
@@ -3844,16 +3847,16 @@
         <v>46225.011180127316</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I45" s="8">
         <v>46260</v>
@@ -3871,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="8">
         <v>46260</v>
@@ -3885,19 +3888,19 @@
       <c r="R45" s="8">
         <v>46260</v>
       </c>
-      <c r="S45" s="10" t="s">
-        <v>31</v>
+      <c r="S45" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
       </c>
-      <c r="U45" s="12" t="s">
-        <v>47</v>
+      <c r="U45" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
@@ -3907,16 +3910,16 @@
         <v>46225.01480951389</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -3934,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -3948,19 +3951,19 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="10" t="s">
-        <v>31</v>
+      <c r="S46" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="12" t="s">
-        <v>47</v>
+      <c r="U46" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" s="8">
         <v>46225.00971478009</v>
@@ -3970,16 +3973,16 @@
         <v>46225.01480953704</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I47" s="8">
         <v>46261</v>
@@ -3997,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47" s="8">
         <v>46261</v>
@@ -4011,19 +4014,19 @@
       <c r="R47" s="8">
         <v>46261</v>
       </c>
-      <c r="S47" s="10" t="s">
-        <v>31</v>
+      <c r="S47" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>47</v>
+      <c r="U47" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
@@ -4033,16 +4036,16 @@
         <v>46225.0148096412</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4060,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4074,19 +4077,19 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="10" t="s">
-        <v>31</v>
+      <c r="S48" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>47</v>
+      <c r="U48" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B49" s="8">
         <v>46225.00973607639</v>
@@ -4096,7 +4099,7 @@
         <v>46225.00984827546</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4120,7 +4123,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4133,7 +4136,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4143,16 +4146,16 @@
         <v>46225.01481001158</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4170,13 +4173,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4184,19 +4187,19 @@
       <c r="R50" s="5">
         <v>46262</v>
       </c>
-      <c r="S50" s="10" t="s">
-        <v>31</v>
+      <c r="S50" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>47</v>
+      <c r="U50" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="8">
         <v>46225.00974854166</v>
@@ -4206,16 +4209,16 @@
         <v>46225.01480996527</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I51" s="8">
         <v>46267</v>
@@ -4233,13 +4236,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q51" s="8">
         <v>46273</v>
@@ -4247,19 +4250,19 @@
       <c r="R51" s="8">
         <v>46267</v>
       </c>
-      <c r="S51" s="10" t="s">
-        <v>31</v>
+      <c r="S51" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>47</v>
+      <c r="U51" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4269,16 +4272,16 @@
         <v>46225.011712824074</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4296,13 +4299,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4312,7 +4315,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" s="8">
         <v>46225.00976584491</v>
@@ -4322,16 +4325,16 @@
         <v>46225.01172789352</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I53" s="8">
         <v>46267</v>
@@ -4349,13 +4352,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4365,7 +4368,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
@@ -4375,16 +4378,16 @@
         <v>46225.01496555556</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4402,13 +4405,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -4416,19 +4419,19 @@
       <c r="R54" s="5">
         <v>46274</v>
       </c>
-      <c r="S54" s="10" t="s">
-        <v>31</v>
+      <c r="S54" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>47</v>
+      <c r="U54" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B55" s="8">
         <v>46225.00981328703</v>
@@ -4438,16 +4441,16 @@
         <v>46225.01220275463</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I55" s="8">
         <v>46274</v>
@@ -4465,13 +4468,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4481,7 +4484,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4491,16 +4494,16 @@
         <v>46225.01221594907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4518,13 +4521,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" s="8">
         <v>46225.00990130787</v>
@@ -4544,7 +4547,7 @@
         <v>46225.010049375</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4568,7 +4571,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4581,7 +4584,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
@@ -4591,16 +4594,16 @@
         <v>46225.01522162037</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4618,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4632,19 +4635,19 @@
       <c r="R58" s="5">
         <v>46230</v>
       </c>
-      <c r="S58" s="10" t="s">
-        <v>31</v>
+      <c r="S58" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>47</v>
+      <c r="U58" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B59" s="8">
         <v>46225.00991375</v>
@@ -4654,16 +4657,16 @@
         <v>46225.01531563657</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I59" s="8">
         <v>46230</v>
@@ -4681,13 +4684,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="8">
         <v>46231</v>
@@ -4695,19 +4698,19 @@
       <c r="R59" s="8">
         <v>46230</v>
       </c>
-      <c r="S59" s="10" t="s">
-        <v>31</v>
+      <c r="S59" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T59" s="9">
         <v>0</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>47</v>
+      <c r="U59" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
@@ -4717,16 +4720,16 @@
         <v>46225.015422638884</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4744,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4758,19 +4761,19 @@
       <c r="R60" s="5">
         <v>46230</v>
       </c>
-      <c r="S60" s="10" t="s">
-        <v>31</v>
+      <c r="S60" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>47</v>
+      <c r="U60" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" s="8">
         <v>46225.009930162036</v>
@@ -4780,7 +4783,7 @@
         <v>46225.01043796296</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -4804,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -4817,7 +4820,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" s="5">
         <v>46225.00993398148</v>
@@ -4827,16 +4830,16 @@
         <v>46225.01512193287</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I62" s="5">
         <v>46275</v>
@@ -4854,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="5">
         <v>46281</v>
@@ -4868,19 +4871,19 @@
       <c r="R62" s="5">
         <v>46275</v>
       </c>
-      <c r="S62" s="10" t="s">
-        <v>31</v>
+      <c r="S62" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>47</v>
+      <c r="U62" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B63" s="8">
         <v>46225.00994118056</v>
@@ -4890,16 +4893,16 @@
         <v>46225.01286980324</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I63" s="8">
         <v>46275</v>
@@ -4917,13 +4920,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46225.009955092595</v>
@@ -4943,16 +4946,16 @@
         <v>46225.01288368055</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I64" s="5">
         <v>46275</v>
@@ -4970,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -4986,7 +4989,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B65" s="8">
         <v>46225.00998927084</v>
@@ -4996,16 +4999,16 @@
         <v>46225.01522188657</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I65" s="8">
         <v>46286</v>
@@ -5023,13 +5026,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q65" s="8">
         <v>46286</v>
@@ -5037,19 +5040,19 @@
       <c r="R65" s="8">
         <v>46286</v>
       </c>
-      <c r="S65" s="10" t="s">
-        <v>31</v>
+      <c r="S65" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>47</v>
+      <c r="U65" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B66" s="5">
         <v>46225.00999641204</v>
@@ -5059,16 +5062,16 @@
         <v>46225.01300766204</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5084,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5100,7 +5103,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B67" s="8">
         <v>46225.01000505787</v>
@@ -5110,16 +5113,16 @@
         <v>46225.013021782404</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5135,13 +5138,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5151,7 +5154,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B68" s="5">
         <v>46225.010088842595</v>
@@ -5161,16 +5164,16 @@
         <v>46225.01531584491</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I68" s="5">
         <v>46287</v>
@@ -5188,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68" s="5">
         <v>46287</v>
@@ -5202,19 +5205,19 @@
       <c r="R68" s="5">
         <v>46287</v>
       </c>
-      <c r="S68" s="10" t="s">
-        <v>31</v>
+      <c r="S68" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>47</v>
+      <c r="U68" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B69" s="8">
         <v>46225.01009811343</v>
@@ -5224,16 +5227,16 @@
         <v>46225.01320763888</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I69" s="8">
         <v>46287</v>
@@ -5251,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5267,7 +5270,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" s="5">
         <v>46225.0101059838</v>
@@ -5277,16 +5280,16 @@
         <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I70" s="5">
         <v>46287</v>
@@ -5304,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5320,7 +5323,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B71" s="8">
         <v>46225.01014195602</v>
@@ -5330,16 +5333,16 @@
         <v>46225.015422881945</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I71" s="8">
         <v>46288</v>
@@ -5357,13 +5360,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q71" s="8">
         <v>46288</v>
@@ -5371,19 +5374,19 @@
       <c r="R71" s="8">
         <v>46288</v>
       </c>
-      <c r="S71" s="10" t="s">
-        <v>31</v>
+      <c r="S71" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T71" s="9">
         <v>0</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>47</v>
+      <c r="U71" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B72" s="5">
         <v>46225.01015462963</v>
@@ -5393,16 +5396,16 @@
         <v>46225.01333716435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I72" s="5">
         <v>46288</v>
@@ -5420,13 +5423,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5436,7 +5439,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B73" s="8">
         <v>46225.01016259259</v>
@@ -5446,16 +5449,16 @@
         <v>46225.01335155092</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I73" s="8">
         <v>46288</v>
@@ -5473,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5489,7 +5492,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B74" s="5">
         <v>46225.01019770833</v>
@@ -5499,16 +5502,16 @@
         <v>46225.0155265162</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -5526,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q74" s="5">
         <v>46289</v>
@@ -5540,19 +5543,19 @@
       <c r="R74" s="5">
         <v>46289</v>
       </c>
-      <c r="S74" s="10" t="s">
-        <v>31</v>
+      <c r="S74" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>47</v>
+      <c r="U74" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B75" s="8">
         <v>46225.010204872684</v>
@@ -5562,16 +5565,16 @@
         <v>46225.013478761575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I75" s="8">
         <v>46289</v>
@@ -5589,13 +5592,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" s="5">
         <v>46225.01021453703</v>
@@ -5615,16 +5618,16 @@
         <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -5642,13 +5645,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B77" s="8">
         <v>46225.0103003125</v>
@@ -5668,16 +5671,16 @@
         <v>46225.01562358796</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I77" s="8">
         <v>46293</v>
@@ -5695,13 +5698,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q77" s="8">
         <v>46293</v>
@@ -5709,19 +5712,19 @@
       <c r="R77" s="8">
         <v>46293</v>
       </c>
-      <c r="S77" s="10" t="s">
-        <v>31</v>
+      <c r="S77" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T77" s="9">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>47</v>
+      <c r="U77" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B78" s="5">
         <v>46225.01030866898</v>
@@ -5731,16 +5734,16 @@
         <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I78" s="5">
         <v>46293</v>
@@ -5758,13 +5761,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5774,7 +5777,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B79" s="8">
         <v>46225.010315949075</v>
@@ -5784,16 +5787,16 @@
         <v>46225.01367180556</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I79" s="8">
         <v>46293</v>
@@ -5811,13 +5814,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B80" s="5">
         <v>46225.010349062504</v>
@@ -5837,7 +5840,7 @@
         <v>46225.010597650464</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -5861,7 +5864,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -5874,7 +5877,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B81" s="8">
         <v>46225.010352893514</v>
@@ -5884,16 +5887,16 @@
         <v>46225.58761383102</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I81" s="8">
         <v>46294</v>
@@ -5911,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="8">
         <v>46294</v>
@@ -5925,19 +5928,19 @@
       <c r="R81" s="8">
         <v>46294</v>
       </c>
-      <c r="S81" s="10" t="s">
-        <v>31</v>
+      <c r="S81" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>47</v>
+      <c r="U81" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B82" s="5">
         <v>46225.010361319444</v>
@@ -5947,16 +5950,16 @@
         <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I82" s="5">
         <v>46294</v>
@@ -5974,13 +5977,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -5990,7 +5993,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B83" s="8">
         <v>46225.0103680787</v>
@@ -6000,16 +6003,16 @@
         <v>46225.01379511574</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I83" s="8">
         <v>46294</v>
@@ -6027,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6043,7 +6046,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B84" s="5">
         <v>46225.010400983796</v>
@@ -6053,16 +6056,16 @@
         <v>46225.587646631946</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I84" s="5">
         <v>46295</v>
@@ -6080,10 +6083,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6094,19 +6097,19 @@
       <c r="R84" s="5">
         <v>46295</v>
       </c>
-      <c r="S84" s="10" t="s">
-        <v>31</v>
+      <c r="S84" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="12" t="s">
-        <v>47</v>
+      <c r="U84" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B85" s="8">
         <v>46225.010407800924</v>
@@ -6116,16 +6119,16 @@
         <v>46225.013919687495</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I85" s="8">
         <v>46295</v>
@@ -6143,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6159,7 +6162,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B86" s="5">
         <v>46225.010414502314</v>
@@ -6169,16 +6172,16 @@
         <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I86" s="5">
         <v>46295</v>
@@ -6196,13 +6199,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6212,7 +6215,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B87" s="8">
         <v>46225.01048866898</v>
@@ -6222,16 +6225,16 @@
         <v>46225.58766351852</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I87" s="8">
         <v>46296</v>
@@ -6249,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q87" s="8">
         <v>46296</v>
@@ -6263,19 +6266,19 @@
       <c r="R87" s="8">
         <v>46296</v>
       </c>
-      <c r="S87" s="10" t="s">
-        <v>31</v>
+      <c r="S87" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>47</v>
+      <c r="U87" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B88" s="5">
         <v>46225.01049565972</v>
@@ -6285,16 +6288,16 @@
         <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6312,13 +6315,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6328,7 +6331,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B89" s="8">
         <v>46225.01050163194</v>
@@ -6338,16 +6341,16 @@
         <v>46225.014061504626</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I89" s="8">
         <v>46296</v>
@@ -6365,13 +6368,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6381,7 +6384,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B90" s="5">
         <v>46225.01053885417</v>
@@ -6391,16 +6394,16 @@
         <v>46225.587682592595</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I90" s="5">
         <v>46297</v>
@@ -6418,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q90" s="5">
         <v>46297</v>
@@ -6432,19 +6435,19 @@
       <c r="R90" s="5">
         <v>46297</v>
       </c>
-      <c r="S90" s="10" t="s">
-        <v>31</v>
+      <c r="S90" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="U90" s="12" t="s">
-        <v>47</v>
+      <c r="U90" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B91" s="8">
         <v>46225.01054688657</v>
@@ -6454,16 +6457,16 @@
         <v>46225.014210312496</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I91" s="8">
         <v>46297</v>
@@ -6481,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6497,7 +6500,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B92" s="5">
         <v>46225.010553252316</v>
@@ -6507,16 +6510,16 @@
         <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>
@@ -6534,13 +6537,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6550,7 +6553,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B93" s="8">
         <v>46225.010582800925</v>
@@ -6560,7 +6563,7 @@
         <v>46225.010649097225</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -6584,7 +6587,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -6597,7 +6600,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B94" s="5">
         <v>46225.01058614583</v>
@@ -6607,16 +6610,16 @@
         <v>46225.01625800926</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I94" s="5">
         <v>46300</v>
@@ -6634,13 +6637,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q94" s="5">
         <v>46304</v>
@@ -6648,19 +6651,19 @@
       <c r="R94" s="5">
         <v>46300</v>
       </c>
-      <c r="S94" s="10" t="s">
-        <v>31</v>
+      <c r="S94" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>47</v>
+      <c r="U94" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B95" s="8">
         <v>46225.01062565972</v>
@@ -6670,7 +6673,7 @@
         <v>46225.01625788194</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -6697,13 +6700,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q95" s="8">
         <v>46304</v>
@@ -6711,14 +6714,14 @@
       <c r="R95" s="8">
         <v>46300</v>
       </c>
-      <c r="S95" s="10" t="s">
-        <v>31</v>
+      <c r="S95" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="T95" s="9">
         <v>0</v>
       </c>
-      <c r="U95" s="12" t="s">
-        <v>47</v>
+      <c r="U95" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46227.73872289352</v>
+        <v>46230.74566054398</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>44</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="285">
   <si>
     <t>50001579- "XEMORTIZ C. MEXICANA"</t>
   </si>
@@ -397,28 +397,34 @@
     <t>Plano Preliminar OT 4377</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1216774111324796</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225605038</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1216774111324796</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225605038</t>
   </si>
   <si>
     <t>Ingenieria y diseñoo:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Propuesta Fabricación externa OT 4377,Propuesta MecanizadoOT 4377,Propuesta Corte plasma  OT 4377,propuesta Corte laserOT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
@@ -3322,7 +3328,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46227.18530354167</v>
+        <v>46231.54237934027</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>127</v>
@@ -3385,7 +3391,7 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46225.01104386574</v>
+        <v>46231.54240399305</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -3457,10 +3463,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3484,7 +3490,7 @@
         <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3504,7 +3510,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46225.00957443287</v>
@@ -3514,16 +3520,16 @@
         <v>46225.01576019676</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I39" s="8">
         <v>46290</v>
@@ -3544,7 +3550,7 @@
         <v>124</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>124</v>
@@ -3567,7 +3573,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3577,16 +3583,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3602,13 +3608,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3618,7 +3624,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46225.00958684028</v>
@@ -3628,16 +3634,16 @@
         <v>46225.01157688657</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="8">
@@ -3653,13 +3659,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3669,7 +3675,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3679,7 +3685,7 @@
         <v>46225.009844733795</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3703,7 +3709,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3716,7 +3722,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46225.00968099537</v>
@@ -3726,16 +3732,16 @@
         <v>46225.011108125</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3751,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="8">
         <v>46260</v>
@@ -3777,7 +3783,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
@@ -3787,16 +3793,16 @@
         <v>46225.01115158565</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3814,13 +3820,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3840,7 +3846,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46225.00969839121</v>
@@ -3850,16 +3856,16 @@
         <v>46225.011180127316</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I45" s="8">
         <v>46260</v>
@@ -3877,13 +3883,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="8">
         <v>46260</v>
@@ -3903,7 +3909,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
@@ -3913,7 +3919,7 @@
         <v>46225.01480951389</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -3940,13 +3946,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -3966,7 +3972,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46225.00971478009</v>
@@ -3976,7 +3982,7 @@
         <v>46225.01480953704</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
@@ -4003,13 +4009,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46261</v>
@@ -4029,7 +4035,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
@@ -4039,7 +4045,7 @@
         <v>46225.0148096412</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4066,13 +4072,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4092,7 +4098,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46225.00973607639</v>
@@ -4102,7 +4108,7 @@
         <v>46225.00984827546</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4126,7 +4132,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4139,7 +4145,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4155,10 +4161,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4176,13 +4182,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4202,7 +4208,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46225.00974854166</v>
@@ -4212,16 +4218,16 @@
         <v>46225.01480996527</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I51" s="8">
         <v>46267</v>
@@ -4239,13 +4245,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q51" s="8">
         <v>46273</v>
@@ -4265,7 +4271,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4275,16 +4281,16 @@
         <v>46225.011712824074</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4302,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4318,7 +4324,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B53" s="8">
         <v>46225.00976584491</v>
@@ -4328,16 +4334,16 @@
         <v>46225.01172789352</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I53" s="8">
         <v>46267</v>
@@ -4355,13 +4361,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O53" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="P53" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4371,7 +4377,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
@@ -4381,7 +4387,7 @@
         <v>46225.01496555556</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4408,13 +4414,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -4434,7 +4440,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B55" s="8">
         <v>46225.00981328703</v>
@@ -4444,7 +4450,7 @@
         <v>46225.01220275463</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4471,13 +4477,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4487,7 +4493,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4497,7 +4503,7 @@
         <v>46225.01221594907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4524,13 +4530,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4540,7 +4546,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B57" s="8">
         <v>46225.00990130787</v>
@@ -4550,7 +4556,7 @@
         <v>46225.010049375</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4574,7 +4580,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4587,26 +4593,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46225.01522162037</v>
+        <v>46231.171834953704</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4624,13 +4630,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>52</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4650,26 +4656,26 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B59" s="8">
         <v>46225.00991375</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46225.01531563657</v>
+        <v>46231.17183640046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I59" s="8">
         <v>46230</v>
@@ -4687,13 +4693,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>57</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q59" s="8">
         <v>46231</v>
@@ -4713,26 +4719,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46225.015422638884</v>
+        <v>46231.17183277778</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4750,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4776,7 +4782,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B61" s="8">
         <v>46225.009930162036</v>
@@ -4786,7 +4792,7 @@
         <v>46225.01043796296</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -4810,7 +4816,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -4823,7 +4829,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46225.00993398148</v>
@@ -4833,7 +4839,7 @@
         <v>46225.01512193287</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4860,13 +4866,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q62" s="5">
         <v>46281</v>
@@ -4886,7 +4892,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B63" s="8">
         <v>46225.00994118056</v>
@@ -4896,7 +4902,7 @@
         <v>46225.01286980324</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -4923,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -4939,7 +4945,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46225.009955092595</v>
@@ -4949,7 +4955,7 @@
         <v>46225.01288368055</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -4976,13 +4982,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -4992,7 +4998,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B65" s="8">
         <v>46225.00998927084</v>
@@ -5002,7 +5008,7 @@
         <v>46225.01522188657</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5029,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q65" s="8">
         <v>46286</v>
@@ -5055,7 +5061,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B66" s="5">
         <v>46225.00999641204</v>
@@ -5065,7 +5071,7 @@
         <v>46225.01300766204</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5090,13 +5096,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5106,7 +5112,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B67" s="8">
         <v>46225.01000505787</v>
@@ -5116,7 +5122,7 @@
         <v>46225.013021782404</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5141,13 +5147,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5157,7 +5163,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46225.010088842595</v>
@@ -5167,7 +5173,7 @@
         <v>46225.01531584491</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5194,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="5">
         <v>46287</v>
@@ -5220,7 +5226,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B69" s="8">
         <v>46225.01009811343</v>
@@ -5230,7 +5236,7 @@
         <v>46225.01320763888</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5257,13 +5263,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5273,7 +5279,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B70" s="5">
         <v>46225.0101059838</v>
@@ -5283,7 +5289,7 @@
         <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5310,13 +5316,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5326,7 +5332,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B71" s="8">
         <v>46225.01014195602</v>
@@ -5336,7 +5342,7 @@
         <v>46225.015422881945</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5363,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q71" s="8">
         <v>46288</v>
@@ -5389,7 +5395,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B72" s="5">
         <v>46225.01015462963</v>
@@ -5399,7 +5405,7 @@
         <v>46225.01333716435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5426,13 +5432,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5442,7 +5448,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B73" s="8">
         <v>46225.01016259259</v>
@@ -5452,7 +5458,7 @@
         <v>46225.01335155092</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5479,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5495,7 +5501,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B74" s="5">
         <v>46225.01019770833</v>
@@ -5505,7 +5511,7 @@
         <v>46225.0155265162</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5532,13 +5538,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q74" s="5">
         <v>46289</v>
@@ -5558,7 +5564,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B75" s="8">
         <v>46225.010204872684</v>
@@ -5568,7 +5574,7 @@
         <v>46225.013478761575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5595,13 +5601,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -5611,7 +5617,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B76" s="5">
         <v>46225.01021453703</v>
@@ -5621,7 +5627,7 @@
         <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5648,13 +5654,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5664,7 +5670,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B77" s="8">
         <v>46225.0103003125</v>
@@ -5674,7 +5680,7 @@
         <v>46225.01562358796</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5701,13 +5707,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q77" s="8">
         <v>46293</v>
@@ -5727,7 +5733,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B78" s="5">
         <v>46225.01030866898</v>
@@ -5737,7 +5743,7 @@
         <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5764,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5780,7 +5786,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B79" s="8">
         <v>46225.010315949075</v>
@@ -5790,7 +5796,7 @@
         <v>46225.01367180556</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -5817,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5833,7 +5839,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B80" s="5">
         <v>46225.010349062504</v>
@@ -5843,7 +5849,7 @@
         <v>46225.010597650464</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -5867,7 +5873,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -5880,7 +5886,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B81" s="8">
         <v>46225.010352893514</v>
@@ -5890,16 +5896,16 @@
         <v>46225.58761383102</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46294</v>
@@ -5917,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q81" s="8">
         <v>46294</v>
@@ -5943,7 +5949,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B82" s="5">
         <v>46225.010361319444</v>
@@ -5953,16 +5959,16 @@
         <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46294</v>
@@ -5980,13 +5986,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -5996,7 +6002,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B83" s="8">
         <v>46225.0103680787</v>
@@ -6006,16 +6012,16 @@
         <v>46225.01379511574</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46294</v>
@@ -6033,13 +6039,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6049,7 +6055,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46225.010400983796</v>
@@ -6059,7 +6065,7 @@
         <v>46225.587646631946</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6086,10 +6092,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6112,7 +6118,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B85" s="8">
         <v>46225.010407800924</v>
@@ -6122,7 +6128,7 @@
         <v>46225.013919687495</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6149,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6165,7 +6171,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46225.010414502314</v>
@@ -6175,7 +6181,7 @@
         <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6202,13 +6208,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6218,7 +6224,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B87" s="8">
         <v>46225.01048866898</v>
@@ -6228,16 +6234,16 @@
         <v>46225.58766351852</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I87" s="8">
         <v>46296</v>
@@ -6255,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q87" s="8">
         <v>46296</v>
@@ -6281,7 +6287,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
         <v>46225.01049565972</v>
@@ -6291,16 +6297,16 @@
         <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6318,13 +6324,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6334,7 +6340,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B89" s="8">
         <v>46225.01050163194</v>
@@ -6344,16 +6350,16 @@
         <v>46225.014061504626</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I89" s="8">
         <v>46296</v>
@@ -6371,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6387,7 +6393,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B90" s="5">
         <v>46225.01053885417</v>
@@ -6397,16 +6403,16 @@
         <v>46225.587682592595</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I90" s="5">
         <v>46297</v>
@@ -6424,13 +6430,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q90" s="5">
         <v>46297</v>
@@ -6450,7 +6456,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B91" s="8">
         <v>46225.01054688657</v>
@@ -6460,16 +6466,16 @@
         <v>46225.014210312496</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I91" s="8">
         <v>46297</v>
@@ -6487,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6503,7 +6509,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
         <v>46225.010553252316</v>
@@ -6513,16 +6519,16 @@
         <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>
@@ -6540,13 +6546,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6556,7 +6562,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B93" s="8">
         <v>46225.010582800925</v>
@@ -6566,7 +6572,7 @@
         <v>46225.010649097225</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -6590,7 +6596,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -6603,7 +6609,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B94" s="5">
         <v>46225.01058614583</v>
@@ -6613,16 +6619,16 @@
         <v>46225.01625800926</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I94" s="5">
         <v>46300</v>
@@ -6640,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46304</v>
@@ -6666,7 +6672,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B95" s="8">
         <v>46225.01062565972</v>
@@ -6676,7 +6682,7 @@
         <v>46225.01625788194</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -6703,13 +6709,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q95" s="8">
         <v>46304</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="299">
   <si>
     <t>50001579- "XEMORTIZ C. MEXICANA"</t>
   </si>
@@ -94,6 +94,9 @@
     <t/>
   </si>
   <si>
+    <t>Tarea Terminada</t>
+  </si>
+  <si>
     <t>1216774205554605</t>
   </si>
   <si>
@@ -109,117 +112,148 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>1216774205554623</t>
+  </si>
+  <si>
+    <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t>1216774244989628</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1579 se tienen 2 ventiladores ZVN 1-9-86/2 para Xemortiz (C. Mexicana):
+    Planos para fabricación O/4377:
+        Ventilador ZVN 1-9-86/2 con motor WEG
+        Alcance: Tobera + Rejilla Concretica + Tipo A 900mm
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+    Fecha de entrega: 01-09-2026
+    Incoterms: EXW
+Quedo atenta
+Saludos,</t>
+  </si>
+  <si>
+    <t>1216774244989646</t>
+  </si>
+  <si>
+    <t>Definicion Tecnica de componentes principales</t>
+  </si>
+  <si>
+    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377,Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1216774094321288</t>
+  </si>
+  <si>
+    <t>Plazo Contractual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Fecha de entrega: 01-09-2026
+    Incoterms: EXW
+</t>
+  </si>
+  <si>
+    <t>1216769310026487</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1216774225564664</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT 4377,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1216769310026489</t>
+  </si>
+  <si>
+    <t>Reservas</t>
+  </si>
+  <si>
+    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377</t>
+  </si>
+  <si>
+    <t>1216774205614949</t>
+  </si>
+  <si>
+    <t>Reserva Alabes OT 4377</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservas,Recepcion Alabe OT 4377 </t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1216774205554623</t>
-  </si>
-  <si>
-    <t>Apertura pedido</t>
-  </si>
-  <si>
-    <t>1216774244989628</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
-  </si>
-  <si>
-    <t>1216774244989646</t>
-  </si>
-  <si>
-    <t>Definicion Tecnica de componentes principales</t>
-  </si>
-  <si>
-    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377,Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1216774094321288</t>
-  </si>
-  <si>
-    <t>Plazo Contractual</t>
-  </si>
-  <si>
-    <t>1216769310026487</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1216774225564664</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT 4377,Ingenieria Jefe de proyecto:</t>
+    <t>1216774205614977</t>
+  </si>
+  <si>
+    <t>Reserva rodeteOT 4377</t>
+  </si>
+  <si>
+    <t>Reservas,Recepcion Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774094321844</t>
+  </si>
+  <si>
+    <t>Reserva motor  OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservas,Recepcion motor OT 4377 </t>
+  </si>
+  <si>
+    <t>1216769310026491</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta Corte laserOT 4377</t>
+  </si>
+  <si>
+    <t>1216774111288068</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC corte laser  OT 4377</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1216769310026489</t>
-  </si>
-  <si>
-    <t>Reservas</t>
-  </si>
-  <si>
-    <t>Reserva rodeteOT 4377,Reserva motor  OT 4377,Reserva Alabes OT 4377</t>
-  </si>
-  <si>
-    <t>1216774205614949</t>
-  </si>
-  <si>
-    <t>Reserva Alabes OT 4377</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservas,Recepcion Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774205614977</t>
-  </si>
-  <si>
-    <t>Reserva rodeteOT 4377</t>
-  </si>
-  <si>
-    <t>Reservas,Recepcion Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>1216774094321844</t>
-  </si>
-  <si>
-    <t>Reserva motor  OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservas,Recepcion motor OT 4377 </t>
-  </si>
-  <si>
-    <t>1216769310026491</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta Corte laserOT 4377</t>
-  </si>
-  <si>
-    <t>1216774111288068</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC corte laser  OT 4377</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
     <t>1216774111289151</t>
   </si>
   <si>
@@ -625,7 +659,19 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Pruebas FAT OT 4377 ,RE-PINTADO OT 4377,Montaje Alabe OT 4377 ,Revestimiento OT 4377 ,Montaje motor OT 4377 ,Montaje Rodete OT 4377</t>
+    <t>Montaje Alabe OT 4377 ,Revestimiento OT 4377 ,Montaje motor OT 4377 ,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216992723280852</t>
+  </si>
+  <si>
+    <t>Conexión eléctrica OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje motor OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas FAT OT 4377 </t>
   </si>
   <si>
     <t>1216774225731680</t>
@@ -634,6 +680,9 @@
     <t xml:space="preserve">Revestimiento OT 4377 </t>
   </si>
   <si>
+    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
     <t>1216774225731703</t>
   </si>
   <si>
@@ -652,6 +701,12 @@
     <t xml:space="preserve">Montaje Alabe OT 4377 </t>
   </si>
   <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Revestimiento OT 4377 </t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
     <t>1216774205782721</t>
   </si>
   <si>
@@ -673,6 +728,12 @@
     <t>Montaje Rodete OT 4377</t>
   </si>
   <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje motor OT 4377 </t>
+  </si>
+  <si>
     <t>1216774245203557</t>
   </si>
   <si>
@@ -691,7 +752,10 @@
     <t>1216774225768105</t>
   </si>
   <si>
-    <t xml:space="preserve">Montaje motor OT 4377 </t>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>Montaje:,Conexión eléctrica OT 4377</t>
   </si>
   <si>
     <t>1216774225770290</t>
@@ -712,7 +776,10 @@
     <t>1216774111516366</t>
   </si>
   <si>
-    <t xml:space="preserve">Pruebas FAT OT 4377 </t>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Conexión eléctrica OT 4377</t>
+  </si>
+  <si>
+    <t>RE-PINTADO OT 4377</t>
   </si>
   <si>
     <t>1216774111524712</t>
@@ -730,7 +797,7 @@
     <t>1216774245306925</t>
   </si>
   <si>
-    <t>RE-PINTADO OT 4377</t>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Pruebas FAT OT 4377 </t>
   </si>
   <si>
     <t>1216774111540892</t>
@@ -919,6 +986,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF62d26f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
@@ -935,11 +1007,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFeec300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
   </fills>
@@ -1000,8 +1067,8 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1389,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:U96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1494,9 +1561,11 @@
       <c r="B4" s="5">
         <v>46225.009180567125</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5">
+        <v>46232.54222043982</v>
+      </c>
       <c r="D4" s="5">
-        <v>46225.009453391205</v>
+        <v>46232.54223384259</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1531,68 +1600,74 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
+      <c r="T4" s="6">
+        <v>1</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46225.00931974537</v>
+      </c>
+      <c r="C5" s="9">
+        <v>46232.54192577546</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46232.541950405095</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>46225</v>
+      </c>
+      <c r="R5" s="9">
+        <v>46225</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="10">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="8">
-        <v>46225.00931974537</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8">
-        <v>46226.202111631945</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="8">
-        <v>46225</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>46225</v>
-      </c>
-      <c r="R5" s="8">
-        <v>46225</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="9">
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1602,9 +1677,11 @@
       <c r="B6" s="5">
         <v>46225.00932652778</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5">
+        <v>46232.54193278935</v>
+      </c>
       <c r="D6" s="5">
-        <v>46226.2021175463</v>
+        <v>46232.54194570602</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1613,10 +1690,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="5">
@@ -1646,99 +1723,103 @@
       <c r="R6" s="5">
         <v>46225</v>
       </c>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46225.00933238426</v>
+      </c>
+      <c r="C7" s="9">
+        <v>46232.54194717592</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46232.54196503472</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="11" t="s">
+      <c r="I7" s="10"/>
+      <c r="J7" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>46225</v>
+      </c>
+      <c r="R7" s="9">
+        <v>46225</v>
+      </c>
+      <c r="S7" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8">
-        <v>46225.00933238426</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8">
-        <v>46226.20211158565</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8">
-        <v>46225</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>46225</v>
-      </c>
-      <c r="R7" s="8">
-        <v>46225</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="9">
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="s">
-        <v>32</v>
+      <c r="T7" s="10">
+        <v>1</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5">
         <v>46225.00933765047</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46232.542199386575</v>
+      </c>
       <c r="D8" s="5">
-        <v>46226.202111875</v>
+        <v>46232.54222103009</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="5">
@@ -1748,7 +1829,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1760,7 +1841,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="5">
         <v>46225</v>
@@ -1768,90 +1849,94 @@
       <c r="R8" s="5">
         <v>46225</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="S8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46225.0093434375</v>
+      </c>
+      <c r="C9" s="9">
+        <v>46232.54196390046</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46232.542277037035</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="11" t="s">
+      <c r="I9" s="10"/>
+      <c r="J9" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>46225</v>
+      </c>
+      <c r="R9" s="9">
+        <v>46225</v>
+      </c>
+      <c r="S9" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="8">
-        <v>46225.0093434375</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8">
-        <v>46226.20211157408</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="8">
-        <v>46225</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>46225</v>
-      </c>
-      <c r="R9" s="8">
-        <v>46225</v>
-      </c>
-      <c r="S9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="9">
-        <v>0</v>
-      </c>
-      <c r="U9" s="11" t="s">
-        <v>32</v>
+      <c r="T9" s="10">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5">
         <v>46225.009185567134</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46232.5427602662</v>
+      </c>
       <c r="D10" s="5">
-        <v>46225.00945684028</v>
+        <v>46232.54277384259</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -1875,7 +1960,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -1883,75 +1968,81 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46225.0093491088</v>
+      </c>
+      <c r="C11" s="9">
+        <v>46232.54274256944</v>
+      </c>
+      <c r="D11" s="9">
+        <v>46232.54276053241</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="9">
+        <v>46226</v>
+      </c>
+      <c r="J11" s="9">
+        <v>46226</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="8">
-        <v>46225.0093491088</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8">
-        <v>46230.74566054398</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="O11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="9">
         <v>46226</v>
       </c>
-      <c r="J11" s="8">
+      <c r="R11" s="9">
         <v>46226</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>46226</v>
-      </c>
-      <c r="R11" s="8">
-        <v>46226</v>
-      </c>
-      <c r="S11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10" t="s">
-        <v>47</v>
+      <c r="S11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="10">
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="5">
         <v>46225.0091897338</v>
@@ -1961,7 +2052,7 @@
         <v>46225.00945758102</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>25</v>
@@ -1985,7 +2076,7 @@
         <v>26</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>26</v>
@@ -1997,90 +2088,90 @@
       <c r="U12" s="6"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="9">
         <v>46225.009357546296</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8">
-        <v>46228.20152732639</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="C13" s="10"/>
+      <c r="D13" s="9">
+        <v>46232.54222844908</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="8">
+      <c r="H13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="9">
         <v>46226</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="9">
         <v>46227</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q13" s="8">
+      <c r="K13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="9">
         <v>46227</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="9">
         <v>46226</v>
       </c>
-      <c r="S13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" s="9">
+      <c r="S13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="10">
         <v>0</v>
       </c>
-      <c r="U13" s="10" t="s">
-        <v>47</v>
+      <c r="U13" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5">
         <v>46225.00936541667</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46228.20152952547</v>
+        <v>46232.5422284375</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I14" s="5">
         <v>46226</v>
@@ -2098,13 +2189,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="5">
         <v>46227</v>
@@ -2112,82 +2203,82 @@
       <c r="R14" s="5">
         <v>46226</v>
       </c>
-      <c r="S14" s="10" t="s">
-        <v>31</v>
+      <c r="S14" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="10" t="s">
-        <v>47</v>
+      <c r="U14" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="9">
         <v>46225.009373043984</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8">
-        <v>46228.2015269213</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="C15" s="10"/>
+      <c r="D15" s="9">
+        <v>46232.54222858796</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="8">
+      <c r="H15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="9">
         <v>46226</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <v>46227</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q15" s="8">
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q15" s="9">
         <v>46227</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="9">
         <v>46226</v>
       </c>
-      <c r="S15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" s="9">
+      <c r="S15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="10" t="s">
-        <v>47</v>
+      <c r="U15" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>46225.00919548611</v>
@@ -2197,7 +2288,7 @@
         <v>46225.00945971065</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2221,7 +2312,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2233,71 +2324,71 @@
       <c r="U16" s="6"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46225.00938174769</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <v>46225.01046802083</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J17" s="9">
+        <v>46246</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="8">
-        <v>46225.00938174769</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8">
-        <v>46225.01046802083</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="O17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>46246</v>
+      </c>
+      <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="J17" s="8">
-        <v>46246</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>46246</v>
-      </c>
-      <c r="R17" s="8">
-        <v>46245</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T17" s="9">
+      <c r="S17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="10" t="s">
-        <v>47</v>
+      <c r="U17" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46225.009388923616</v>
@@ -2307,16 +2398,16 @@
         <v>46225.010489479166</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I18" s="5">
         <v>46245</v>
@@ -2334,13 +2425,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2348,82 +2439,82 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>68</v>
+      <c r="S18" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="10" t="s">
-        <v>47</v>
+      <c r="U18" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="9">
         <v>46225.009394699075</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8">
+      <c r="C19" s="10"/>
+      <c r="D19" s="9">
         <v>46225.010513518515</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="E19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="8">
+      <c r="H19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="9">
         <v>46245</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="9">
         <v>46246</v>
       </c>
-      <c r="K19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q19" s="8">
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q19" s="9">
         <v>46246</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T19" s="9">
+      <c r="S19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="10" t="s">
-        <v>47</v>
+      <c r="U19" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B20" s="5">
         <v>46225.00940033565</v>
@@ -2433,16 +2524,16 @@
         <v>46225.010537939816</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I20" s="5">
         <v>46245</v>
@@ -2460,13 +2551,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2474,66 +2565,66 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>68</v>
+      <c r="S20" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="10" t="s">
-        <v>47</v>
+      <c r="U20" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="A21" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="9">
         <v>46225.00920047454</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8">
+      <c r="C21" s="10"/>
+      <c r="D21" s="9">
         <v>46225.00964425926</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="E21" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="9" t="s">
+      <c r="G21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
+      <c r="N21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" s="5">
         <v>46225.00940686342</v>
@@ -2543,16 +2634,16 @@
         <v>46225.01056048612</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2570,13 +2661,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2584,78 +2675,78 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>68</v>
+      <c r="S22" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="10" t="s">
-        <v>47</v>
+      <c r="U22" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46225.00941383102</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9">
+        <v>46225.01069787037</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="8">
-        <v>46225.00941383102</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8">
-        <v>46225.01069787037</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="H23" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="9" t="s">
+      <c r="I23" s="9">
+        <v>46247</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46248</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I23" s="8">
-        <v>46247</v>
-      </c>
-      <c r="J23" s="8">
-        <v>46248</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T23" s="9">
+      <c r="O23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="10" t="s">
-        <v>47</v>
+      <c r="U23" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46225.00942686343</v>
@@ -2665,16 +2756,16 @@
         <v>46225.010714247685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2692,92 +2783,92 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="12" t="s">
-        <v>68</v>
+      <c r="S24" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="10" t="s">
-        <v>47</v>
+      <c r="U24" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="8">
+      <c r="A25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="9">
         <v>46225.00943440972</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8">
+      <c r="C25" s="10"/>
+      <c r="D25" s="9">
         <v>46225.01060155092</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="9" t="s">
+      <c r="E25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46247</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46259</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="O25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>46259</v>
+      </c>
+      <c r="R25" s="9">
         <v>46247</v>
       </c>
-      <c r="J25" s="8">
-        <v>46259</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>46259</v>
-      </c>
-      <c r="R25" s="8">
-        <v>46247</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T25" s="9">
+      <c r="S25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="10" t="s">
-        <v>47</v>
+      <c r="U25" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46225.00944026621</v>
@@ -2787,16 +2878,16 @@
         <v>46225.010778923606</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -2814,13 +2905,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2829,61 +2920,61 @@
       <c r="U26" s="6"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="8">
+      <c r="A27" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="9">
         <v>46225.0094466088</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8">
+      <c r="C27" s="10"/>
+      <c r="D27" s="9">
         <v>46225.010798159725</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="E27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="9">
         <v>46251</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="9">
         <v>46259</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
+      <c r="K27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46225.00949415509</v>
@@ -2893,16 +2984,16 @@
         <v>46225.01062606482</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -2920,10 +3011,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -2934,72 +3025,72 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>68</v>
+      <c r="S28" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="10" t="s">
-        <v>47</v>
+      <c r="U28" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="A29" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="9">
         <v>46225.00950069445</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8">
+      <c r="C29" s="10"/>
+      <c r="D29" s="9">
         <v>46225.01085252315</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="E29" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="9">
         <v>46247</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="9">
         <v>46248</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="P29" s="9" t="s">
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
+      <c r="O29" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46225.00950701389</v>
@@ -3009,16 +3100,16 @@
         <v>46225.01087347222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3036,13 +3127,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3051,71 +3142,71 @@
       <c r="U30" s="6"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="9">
         <v>46225.009512488425</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="8">
+      <c r="C31" s="10"/>
+      <c r="D31" s="9">
         <v>46225.01064516204</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="E31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I31" s="9">
         <v>46247</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="9">
         <v>46289</v>
       </c>
-      <c r="K31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q31" s="8">
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="9">
         <v>46289</v>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="9">
         <v>46247</v>
       </c>
-      <c r="S31" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T31" s="9">
+      <c r="S31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T31" s="10">
         <v>0</v>
       </c>
-      <c r="U31" s="10" t="s">
-        <v>47</v>
+      <c r="U31" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3125,16 +3216,16 @@
         <v>46225.01092217593</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3152,13 +3243,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3167,61 +3258,61 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46225.0095310301</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9">
+        <v>46225.010939224536</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="9">
+        <v>46258</v>
+      </c>
+      <c r="J33" s="9">
+        <v>46288</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="O33" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="8">
-        <v>46225.0095310301</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="8">
-        <v>46225.010939224536</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I33" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J33" s="8">
-        <v>46288</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
+      <c r="P33" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3231,16 +3322,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3258,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3273,74 +3364,76 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="9">
         <v>46225.00954297454</v>
       </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="8">
-        <v>46225.00964719907</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F35" s="9" t="s">
+      <c r="C35" s="10"/>
+      <c r="D35" s="9">
+        <v>46232.57608709491</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="9" t="s">
+      <c r="G35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
+      <c r="N35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46232.57608151621</v>
+      </c>
       <c r="D36" s="5">
-        <v>46231.54237934027</v>
+        <v>46232.57610162037</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3358,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3372,82 +3465,82 @@
       <c r="R36" s="5">
         <v>46230</v>
       </c>
-      <c r="S36" s="11" t="s">
+      <c r="S36" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="T36" s="6">
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46225.009553993055</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9">
+        <v>46232.57609670139</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="T36" s="6">
+      <c r="H37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I37" s="9">
+        <v>46237</v>
+      </c>
+      <c r="J37" s="9">
+        <v>46241</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R37" s="9">
+        <v>46237</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T37" s="10">
         <v>0</v>
       </c>
-      <c r="U36" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="8">
-        <v>46225.009553993055</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="8">
-        <v>46231.54240399305</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="8">
-        <v>46237</v>
-      </c>
-      <c r="J37" s="8">
-        <v>46241</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q37" s="8">
-        <v>46241</v>
-      </c>
-      <c r="R37" s="8">
-        <v>46237</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T37" s="9">
-        <v>0</v>
-      </c>
-      <c r="U37" s="10" t="s">
-        <v>47</v>
+      <c r="U37" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46225.00956064815</v>
@@ -3457,16 +3550,16 @@
         <v>46225.01522170139</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3484,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3498,82 +3591,82 @@
       <c r="R38" s="5">
         <v>46244</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>68</v>
+      <c r="S38" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="10" t="s">
-        <v>47</v>
+      <c r="U38" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="9">
         <v>46225.00957443287</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="8">
+      <c r="C39" s="10"/>
+      <c r="D39" s="9">
         <v>46225.01576019676</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="I39" s="8">
+      <c r="E39" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I39" s="9">
         <v>46290</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="9">
         <v>46290</v>
       </c>
-      <c r="K39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q39" s="8">
+      <c r="K39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q39" s="9">
         <v>46290</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="9">
         <v>46290</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T39" s="9">
+      <c r="S39" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="10" t="s">
-        <v>47</v>
+      <c r="U39" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3583,16 +3676,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3608,13 +3701,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3623,59 +3716,59 @@
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" s="8">
+      <c r="A41" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="9">
         <v>46225.00958684028</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8">
+      <c r="C41" s="10"/>
+      <c r="D41" s="9">
         <v>46225.01157688657</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="8">
+      <c r="I41" s="10"/>
+      <c r="J41" s="9">
         <v>46290</v>
       </c>
-      <c r="K41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P41" s="9" t="s">
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="O41" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
+      <c r="P41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3685,7 +3778,7 @@
         <v>46225.009844733795</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3709,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3721,69 +3814,69 @@
       <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="9">
         <v>46225.00968099537</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8">
+      <c r="C43" s="10"/>
+      <c r="D43" s="9">
         <v>46225.011108125</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="9">
+        <v>46260</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="8">
+      <c r="O43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q43" s="9">
         <v>46260</v>
       </c>
-      <c r="K43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q43" s="8">
+      <c r="R43" s="9">
         <v>46260</v>
       </c>
-      <c r="R43" s="8">
-        <v>46260</v>
-      </c>
-      <c r="S43" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T43" s="9">
+      <c r="S43" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="10" t="s">
-        <v>47</v>
+      <c r="U43" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
@@ -3793,16 +3886,16 @@
         <v>46225.01115158565</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3820,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3834,82 +3927,82 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>68</v>
+      <c r="S44" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="10" t="s">
-        <v>47</v>
+      <c r="U44" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="9">
         <v>46225.00969839121</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="8">
+      <c r="C45" s="10"/>
+      <c r="D45" s="9">
         <v>46225.011180127316</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="E45" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="9">
         <v>46260</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="9">
         <v>46260</v>
       </c>
-      <c r="K45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q45" s="8">
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q45" s="9">
         <v>46260</v>
       </c>
-      <c r="R45" s="8">
+      <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T45" s="9">
+      <c r="S45" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T45" s="10">
         <v>0</v>
       </c>
-      <c r="U45" s="10" t="s">
-        <v>47</v>
+      <c r="U45" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
@@ -3919,16 +4012,16 @@
         <v>46225.01480951389</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -3946,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -3960,82 +4053,82 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>68</v>
+      <c r="S46" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="10" t="s">
-        <v>47</v>
+      <c r="U46" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="9">
         <v>46225.00971478009</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="8">
+      <c r="C47" s="10"/>
+      <c r="D47" s="9">
         <v>46225.01480953704</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="E47" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I47" s="9">
         <v>46261</v>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="9">
         <v>46261</v>
       </c>
-      <c r="K47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q47" s="8">
+      <c r="K47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q47" s="9">
         <v>46261</v>
       </c>
-      <c r="R47" s="8">
+      <c r="R47" s="9">
         <v>46261</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T47" s="9">
+      <c r="S47" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="10" t="s">
-        <v>47</v>
+      <c r="U47" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
@@ -4045,16 +4138,16 @@
         <v>46225.0148096412</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4072,13 +4165,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4086,66 +4179,66 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>68</v>
+      <c r="S48" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="10" t="s">
-        <v>47</v>
+      <c r="U48" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B49" s="8">
+      <c r="A49" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="9">
         <v>46225.00973607639</v>
       </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="8">
+      <c r="C49" s="10"/>
+      <c r="D49" s="9">
         <v>46225.00984827546</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" s="9" t="s">
+      <c r="E49" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F49" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="9" t="s">
+      <c r="G49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
+      <c r="N49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4155,16 +4248,16 @@
         <v>46225.01481001158</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4182,13 +4275,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4196,82 +4289,82 @@
       <c r="R50" s="5">
         <v>46262</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>68</v>
+      <c r="S50" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="10" t="s">
-        <v>47</v>
+      <c r="U50" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46225.00974854166</v>
+      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="9">
+        <v>46225.01480996527</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="8">
-        <v>46225.00974854166</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="8">
-        <v>46225.01480996527</v>
-      </c>
-      <c r="E51" s="9" t="s">
+      <c r="H51" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="I51" s="9">
+        <v>46267</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46273</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="H51" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I51" s="8">
+      <c r="O51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>46273</v>
+      </c>
+      <c r="R51" s="9">
         <v>46267</v>
       </c>
-      <c r="J51" s="8">
-        <v>46273</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q51" s="8">
-        <v>46273</v>
-      </c>
-      <c r="R51" s="8">
-        <v>46267</v>
-      </c>
-      <c r="S51" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T51" s="9">
+      <c r="S51" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="10" t="s">
-        <v>47</v>
+      <c r="U51" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4281,16 +4374,16 @@
         <v>46225.011712824074</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4308,13 +4401,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4323,61 +4416,61 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B53" s="8">
+      <c r="A53" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" s="9">
         <v>46225.00976584491</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="8">
+      <c r="C53" s="10"/>
+      <c r="D53" s="9">
         <v>46225.01172789352</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I53" s="8">
+      <c r="E53" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I53" s="9">
         <v>46267</v>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="9">
         <v>46273</v>
       </c>
-      <c r="K53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P53" s="9" t="s">
+      <c r="K53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="O53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
@@ -4387,16 +4480,16 @@
         <v>46225.01496555556</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4414,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -4428,72 +4521,72 @@
       <c r="R54" s="5">
         <v>46274</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>68</v>
+      <c r="S54" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="10" t="s">
-        <v>47</v>
+      <c r="U54" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="9">
         <v>46225.00981328703</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="8">
+      <c r="C55" s="10"/>
+      <c r="D55" s="9">
         <v>46225.01220275463</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I55" s="8">
+      <c r="E55" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I55" s="9">
         <v>46274</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="9">
         <v>46274</v>
       </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="P55" s="9" t="s">
+      <c r="K55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="Q55" s="9"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
+      <c r="O55" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4503,16 +4596,16 @@
         <v>46225.01221594907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4530,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4545,74 +4638,74 @@
       <c r="U56" s="6"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B57" s="8">
+      <c r="A57" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B57" s="9">
         <v>46225.00990130787</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="8">
+      <c r="C57" s="10"/>
+      <c r="D57" s="9">
         <v>46225.010049375</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="F57" s="9" t="s">
+      <c r="E57" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F57" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="9" t="s">
+      <c r="G57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="N57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46231.171834953704</v>
+        <v>46232.1720309375</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4630,13 +4723,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4644,101 +4737,101 @@
       <c r="R58" s="5">
         <v>46230</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>68</v>
+      <c r="S58" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="10" t="s">
-        <v>47</v>
+      <c r="U58" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B59" s="9">
         <v>46225.00991375</v>
       </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="8">
-        <v>46231.17183640046</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="C59" s="10"/>
+      <c r="D59" s="9">
+        <v>46232.172030752314</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I59" s="9">
         <v>46230</v>
       </c>
-      <c r="J59" s="8">
+      <c r="J59" s="9">
         <v>46231</v>
       </c>
-      <c r="K59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q59" s="8">
+      <c r="K59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q59" s="9">
         <v>46231</v>
       </c>
-      <c r="R59" s="8">
+      <c r="R59" s="9">
         <v>46230</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T59" s="9">
+      <c r="S59" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" s="10">
         <v>0</v>
       </c>
-      <c r="U59" s="10" t="s">
-        <v>47</v>
+      <c r="U59" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46231.17183277778</v>
+        <v>46232.17203079861</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4756,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4770,201 +4863,199 @@
       <c r="R60" s="5">
         <v>46230</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>68</v>
+      <c r="S60" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="10" t="s">
-        <v>47</v>
+      <c r="U60" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" s="9">
         <v>46225.009930162036</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8">
-        <v>46225.01043796296</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F61" s="9" t="s">
+      <c r="C61" s="10"/>
+      <c r="D61" s="9">
+        <v>46232.62468724537</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="9" t="s">
+      <c r="G61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
+      <c r="N61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46225.00993398148</v>
+        <v>46232.624683587965</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46225.01512193287</v>
+        <v>46232.62478408565</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="5">
+        <v>46289</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46289</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H62" s="6" t="s">
+      <c r="O62" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="9">
+        <v>46225.00993398148</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="9">
+        <v>46232.6243815625</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I62" s="5">
+      <c r="H63" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" s="9">
         <v>46275</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J63" s="9">
         <v>46281</v>
       </c>
-      <c r="K62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q62" s="5">
+      <c r="K63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="O63" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q63" s="9">
         <v>46281</v>
       </c>
-      <c r="R62" s="5">
+      <c r="R63" s="9">
         <v>46275</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T62" s="6">
+      <c r="S63" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U62" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B63" s="8">
-        <v>46225.00994118056</v>
-      </c>
-      <c r="C63" s="9"/>
-      <c r="D63" s="8">
-        <v>46225.01286980324</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I63" s="8">
-        <v>46275</v>
-      </c>
-      <c r="J63" s="8">
-        <v>46281</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q63" s="9"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46225.009955092595</v>
+        <v>46225.00994118056</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46225.01288368055</v>
+        <v>46225.01286980324</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I64" s="5">
         <v>46275</v>
@@ -4982,13 +5073,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -4997,92 +5088,84 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B65" s="8">
-        <v>46225.00998927084</v>
-      </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="8">
-        <v>46225.01522188657</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H65" s="9" t="s">
+      <c r="A65" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B65" s="9">
+        <v>46225.009955092595</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="9">
+        <v>46225.01288368055</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I65" s="8">
-        <v>46286</v>
-      </c>
-      <c r="J65" s="8">
-        <v>46286</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="O65" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q65" s="8">
-        <v>46286</v>
-      </c>
-      <c r="R65" s="8">
-        <v>46286</v>
-      </c>
-      <c r="S65" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T65" s="9">
-        <v>0</v>
-      </c>
-      <c r="U65" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="H65" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I65" s="9">
+        <v>46275</v>
+      </c>
+      <c r="J65" s="9">
+        <v>46281</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B66" s="5">
-        <v>46225.00999641204</v>
+        <v>46225.00998927084</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46225.01300766204</v>
+        <v>46232.62438284722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I66" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="I66" s="5">
+        <v>46286</v>
+      </c>
       <c r="J66" s="5">
         <v>46286</v>
       </c>
@@ -5096,209 +5179,217 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-      <c r="U66" s="6"/>
+        <v>222</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>46286</v>
+      </c>
+      <c r="R66" s="5">
+        <v>46286</v>
+      </c>
+      <c r="S66" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T66" s="6">
+        <v>0</v>
+      </c>
+      <c r="U66" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B67" s="8">
-        <v>46225.01000505787</v>
-      </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="8">
-        <v>46225.013021782404</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H67" s="9" t="s">
+      <c r="A67" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="9">
+        <v>46225.00999641204</v>
+      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="9">
+        <v>46225.01300766204</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="8">
+      <c r="H67" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I67" s="10"/>
+      <c r="J67" s="9">
         <v>46286</v>
       </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q67" s="9"/>
-      <c r="R67" s="9"/>
-      <c r="S67" s="9"/>
-      <c r="T67" s="9"/>
-      <c r="U67" s="9"/>
+      <c r="K67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46225.010088842595</v>
+        <v>46225.01000505787</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46225.01531584491</v>
+        <v>46225.013021782404</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H68" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I68" s="6"/>
+      <c r="J68" s="5">
+        <v>46286</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B69" s="9">
+        <v>46225.010088842595</v>
+      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="9">
+        <v>46232.624382546295</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I68" s="5">
+      <c r="H69" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I69" s="9">
         <v>46287</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J69" s="9">
         <v>46287</v>
       </c>
-      <c r="K68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q68" s="5">
+      <c r="K69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q69" s="9">
         <v>46287</v>
       </c>
-      <c r="R68" s="5">
+      <c r="R69" s="9">
         <v>46287</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T68" s="6">
+      <c r="S69" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T69" s="10">
         <v>0</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B69" s="8">
-        <v>46225.01009811343</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="8">
-        <v>46225.01320763888</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I69" s="8">
-        <v>46287</v>
-      </c>
-      <c r="J69" s="8">
-        <v>46287</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q69" s="9"/>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="9"/>
+      <c r="U69" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
-        <v>46225.0101059838</v>
+        <v>46225.01009811343</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.013223182876</v>
+        <v>46225.01320763888</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I70" s="5">
         <v>46287</v>
@@ -5316,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5331,90 +5422,80 @@
       <c r="U70" s="6"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B71" s="8">
-        <v>46225.01014195602</v>
-      </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="8">
-        <v>46225.015422881945</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H71" s="9" t="s">
+      <c r="A71" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B71" s="9">
+        <v>46225.0101059838</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="9">
+        <v>46225.013223182876</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I71" s="8">
-        <v>46288</v>
-      </c>
-      <c r="J71" s="8">
-        <v>46288</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q71" s="8">
-        <v>46288</v>
-      </c>
-      <c r="R71" s="8">
-        <v>46288</v>
-      </c>
-      <c r="S71" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T71" s="9">
-        <v>0</v>
-      </c>
-      <c r="U71" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="H71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I71" s="9">
+        <v>46287</v>
+      </c>
+      <c r="J71" s="9">
+        <v>46287</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46225.01015462963</v>
+        <v>46225.01014195602</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.01333716435</v>
+        <v>46232.62478408565</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I72" s="5">
         <v>46288</v>
@@ -5432,211 +5513,221 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+        <v>239</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46288</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46288</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T72" s="6">
+        <v>0</v>
+      </c>
+      <c r="U72" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B73" s="8">
-        <v>46225.01016259259</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8">
-        <v>46225.01335155092</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H73" s="9" t="s">
+      <c r="A73" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B73" s="9">
+        <v>46225.01015462963</v>
+      </c>
+      <c r="C73" s="10"/>
+      <c r="D73" s="9">
+        <v>46225.01333716435</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I73" s="8">
+      <c r="H73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" s="9">
         <v>46288</v>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="9">
         <v>46288</v>
       </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q73" s="9"/>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="K73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
-        <v>46225.01019770833</v>
+        <v>46225.01016259259</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46225.0155265162</v>
+        <v>46225.01335155092</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H74" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46288</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46288</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" s="9">
+        <v>46225.01019770833</v>
+      </c>
+      <c r="C75" s="10"/>
+      <c r="D75" s="9">
+        <v>46232.624783935185</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I74" s="5">
+      <c r="H75" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" s="9">
+        <v>46290</v>
+      </c>
+      <c r="J75" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q75" s="9">
         <v>46289</v>
       </c>
-      <c r="J74" s="5">
+      <c r="R75" s="9">
         <v>46289</v>
       </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46289</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46289</v>
-      </c>
-      <c r="S74" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T74" s="6">
+      <c r="S75" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B75" s="8">
-        <v>46225.010204872684</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="8">
-        <v>46225.013478761575</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I75" s="8">
-        <v>46289</v>
-      </c>
-      <c r="J75" s="8">
-        <v>46289</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
+      <c r="U75" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46225.01021453703</v>
+        <v>46225.010204872684</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.01351359954</v>
+        <v>46225.013478761575</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -5654,13 +5745,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5669,90 +5760,80 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B77" s="8">
-        <v>46225.0103003125</v>
-      </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="8">
-        <v>46225.01562358796</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="9" t="s">
+      <c r="A77" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B77" s="9">
+        <v>46225.01021453703</v>
+      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="9">
+        <v>46225.01351359954</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I77" s="8">
-        <v>46293</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46293</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>46293</v>
-      </c>
-      <c r="R77" s="8">
-        <v>46293</v>
-      </c>
-      <c r="S77" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T77" s="9">
-        <v>0</v>
-      </c>
-      <c r="U77" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="H77" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" s="9">
+        <v>46289</v>
+      </c>
+      <c r="J77" s="9">
+        <v>46289</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="O77" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46225.01030866898</v>
+        <v>46225.0103003125</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46225.0136440625</v>
+        <v>46232.624382152775</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I78" s="5">
         <v>46293</v>
@@ -5770,96 +5851,112 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46293</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46293</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46225.010315949075</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46225.01367180556</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H79" s="9" t="s">
+      <c r="A79" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B79" s="9">
+        <v>46225.01030866898</v>
+      </c>
+      <c r="C79" s="10"/>
+      <c r="D79" s="9">
+        <v>46225.0136440625</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I79" s="8">
+      <c r="H79" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="9">
         <v>46293</v>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="9">
         <v>46293</v>
       </c>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
+      <c r="K79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46225.010349062504</v>
+        <v>46225.010315949075</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.010597650464</v>
+        <v>46225.01367180556</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46293</v>
+      </c>
+      <c r="J80" s="5">
+        <v>46293</v>
+      </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
       </c>
@@ -5867,16 +5964,16 @@
         <v>26</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>26</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5885,90 +5982,74 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46225.010352893514</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46225.58761383102</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46294</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46294</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46294</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46294</v>
-      </c>
-      <c r="S81" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T81" s="9">
+      <c r="A81" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" s="9">
+        <v>46225.010349062504</v>
+      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="9">
+        <v>46225.010597650464</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="N81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O81" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46225.010361319444</v>
+        <v>46225.010352893514</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.01378356482</v>
+        <v>46225.58761383102</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>145</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I82" s="5">
         <v>46294</v>
@@ -5986,211 +6067,221 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>46294</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46294</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T82" s="6">
+        <v>0</v>
+      </c>
+      <c r="U82" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B83" s="8">
-        <v>46225.0103680787</v>
-      </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="8">
-        <v>46225.01379511574</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I83" s="8">
+      <c r="A83" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B83" s="9">
+        <v>46225.010361319444</v>
+      </c>
+      <c r="C83" s="10"/>
+      <c r="D83" s="9">
+        <v>46225.01378356482</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="I83" s="9">
         <v>46294</v>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="9">
         <v>46294</v>
       </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q83" s="9"/>
-      <c r="R83" s="9"/>
-      <c r="S83" s="9"/>
-      <c r="T83" s="9"/>
-      <c r="U83" s="9"/>
+      <c r="K83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46225.010400983796</v>
+        <v>46225.0103680787</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
+        <v>46225.01379511574</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46294</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46294</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" s="9">
+        <v>46225.010400983796</v>
+      </c>
+      <c r="C85" s="10"/>
+      <c r="D85" s="9">
         <v>46225.587646631946</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H84" s="6" t="s">
+      <c r="E85" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I84" s="5">
+      <c r="H85" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I85" s="9">
         <v>46295</v>
       </c>
-      <c r="J84" s="5">
+      <c r="J85" s="9">
         <v>46295</v>
       </c>
-      <c r="K84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q84" s="5">
+      <c r="K85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q85" s="9">
         <v>46295</v>
       </c>
-      <c r="R84" s="5">
+      <c r="R85" s="9">
         <v>46295</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T84" s="6">
+      <c r="S85" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T85" s="10">
         <v>0</v>
       </c>
-      <c r="U84" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="B85" s="8">
-        <v>46225.010407800924</v>
-      </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="8">
-        <v>46225.013919687495</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I85" s="8">
-        <v>46295</v>
-      </c>
-      <c r="J85" s="8">
-        <v>46295</v>
-      </c>
-      <c r="K85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
+      <c r="U85" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B86" s="5">
-        <v>46225.010414502314</v>
+        <v>46225.010407800924</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46225.013935787036</v>
+        <v>46225.013919687495</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I86" s="5">
         <v>46295</v>
@@ -6208,13 +6299,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6223,90 +6314,80 @@
       <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B87" s="8">
-        <v>46225.01048866898</v>
-      </c>
-      <c r="C87" s="9"/>
-      <c r="D87" s="8">
-        <v>46225.58766351852</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I87" s="8">
-        <v>46296</v>
-      </c>
-      <c r="J87" s="8">
-        <v>46296</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="O87" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q87" s="8">
-        <v>46296</v>
-      </c>
-      <c r="R87" s="8">
-        <v>46296</v>
-      </c>
-      <c r="S87" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T87" s="9">
-        <v>0</v>
-      </c>
-      <c r="U87" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="A87" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B87" s="9">
+        <v>46225.010414502314</v>
+      </c>
+      <c r="C87" s="10"/>
+      <c r="D87" s="9">
+        <v>46225.013935787036</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I87" s="9">
+        <v>46295</v>
+      </c>
+      <c r="J87" s="9">
+        <v>46295</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="O87" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P87" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46225.01049565972</v>
+        <v>46225.01048866898</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46225.014048425925</v>
+        <v>46225.58766351852</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>145</v>
+        <v>278</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6324,211 +6405,221 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>259</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46296</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46296</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0</v>
+      </c>
+      <c r="U88" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B89" s="8">
-        <v>46225.01050163194</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8">
-        <v>46225.014061504626</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I89" s="8">
+      <c r="A89" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B89" s="9">
+        <v>46225.01049565972</v>
+      </c>
+      <c r="C89" s="10"/>
+      <c r="D89" s="9">
+        <v>46225.014048425925</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I89" s="9">
         <v>46296</v>
       </c>
-      <c r="J89" s="8">
+      <c r="J89" s="9">
         <v>46296</v>
       </c>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+      <c r="K89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B90" s="5">
-        <v>46225.01053885417</v>
+        <v>46225.01050163194</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
+        <v>46225.014061504626</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I90" s="5">
+        <v>46296</v>
+      </c>
+      <c r="J90" s="5">
+        <v>46296</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B91" s="9">
+        <v>46225.01053885417</v>
+      </c>
+      <c r="C91" s="10"/>
+      <c r="D91" s="9">
         <v>46225.587682592595</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I90" s="5">
+      <c r="E91" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I91" s="9">
         <v>46297</v>
       </c>
-      <c r="J90" s="5">
+      <c r="J91" s="9">
         <v>46297</v>
       </c>
-      <c r="K90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q90" s="5">
+      <c r="K91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P91" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q91" s="9">
         <v>46297</v>
       </c>
-      <c r="R90" s="5">
+      <c r="R91" s="9">
         <v>46297</v>
       </c>
-      <c r="S90" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T90" s="6">
+      <c r="S91" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T91" s="10">
         <v>0</v>
       </c>
-      <c r="U90" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B91" s="8">
-        <v>46225.01054688657</v>
-      </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="8">
-        <v>46225.014210312496</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I91" s="8">
-        <v>46297</v>
-      </c>
-      <c r="J91" s="8">
-        <v>46297</v>
-      </c>
-      <c r="K91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q91" s="9"/>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
+      <c r="U91" s="11" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
-        <v>46225.010553252316</v>
+        <v>46225.01054688657</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46225.01422244213</v>
+        <v>46225.014210312496</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>
@@ -6546,13 +6637,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6561,176 +6652,229 @@
       <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B93" s="8">
-        <v>46225.010582800925</v>
-      </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="8">
-        <v>46225.010649097225</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="A93" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B93" s="9">
+        <v>46225.010553252316</v>
+      </c>
+      <c r="C93" s="10"/>
+      <c r="D93" s="9">
+        <v>46225.01422244213</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I93" s="9">
+        <v>46297</v>
+      </c>
+      <c r="J93" s="9">
+        <v>46297</v>
+      </c>
+      <c r="K93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P93" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
-        <v>46225.01058614583</v>
+        <v>46225.010582800925</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
+        <v>46225.010649097225</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A95" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B95" s="9">
+        <v>46225.01058614583</v>
+      </c>
+      <c r="C95" s="10"/>
+      <c r="D95" s="9">
         <v>46225.01625800926</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="I94" s="5">
+      <c r="E95" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="I95" s="9">
         <v>46300</v>
       </c>
-      <c r="J94" s="5">
+      <c r="J95" s="9">
         <v>46304</v>
       </c>
-      <c r="K94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q94" s="5">
+      <c r="K95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="O95" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q95" s="9">
         <v>46304</v>
       </c>
-      <c r="R94" s="5">
+      <c r="R95" s="9">
         <v>46300</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T94" s="6">
+      <c r="S95" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T95" s="10">
         <v>0</v>
       </c>
-      <c r="U94" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B95" s="8">
+      <c r="U95" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B96" s="5">
         <v>46225.01062565972</v>
       </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="8">
+      <c r="C96" s="6"/>
+      <c r="D96" s="5">
         <v>46225.01625788194</v>
       </c>
-      <c r="E95" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H95" s="9" t="s">
+      <c r="E96" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I95" s="8">
+      <c r="H96" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I96" s="5">
         <v>46300</v>
       </c>
-      <c r="J95" s="8">
+      <c r="J96" s="5">
         <v>46304</v>
       </c>
-      <c r="K95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q95" s="8">
+      <c r="K96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q96" s="5">
         <v>46304</v>
       </c>
-      <c r="R95" s="8">
+      <c r="R96" s="5">
         <v>46300</v>
       </c>
-      <c r="S95" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T95" s="9">
+      <c r="S96" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U95" s="10" t="s">
-        <v>47</v>
+      <c r="U96" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46232.57609670139</v>
+        <v>46234.18822325231</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>136</v>
@@ -3528,8 +3528,8 @@
       <c r="R37" s="9">
         <v>46237</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>70</v>
+      <c r="S37" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -440,16 +440,16 @@
     <t>Ingenieria y diseñoo:,Plano Definitivos OT 4377</t>
   </si>
   <si>
+    <t>1216774111324796</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774111324796</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
   </si>
   <si>
     <t>1216774225605038</t>
@@ -3421,7 +3421,7 @@
         <v>46232.57608151621</v>
       </c>
       <c r="D36" s="5">
-        <v>46232.57610162037</v>
+        <v>46235.19777150463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3465,8 +3465,8 @@
       <c r="R36" s="5">
         <v>46230</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>134</v>
+      <c r="S36" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46225.009553993055</v>
@@ -3487,7 +3487,7 @@
         <v>46234.18822325231</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3520,7 +3520,7 @@
         <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3529,7 +3529,7 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>141</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -245,60 +245,63 @@
     <t>Propuesta compras:,Generación OC corte laser  OT 4377</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216774111289151</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111289169</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa OT 4377</t>
+  </si>
+  <si>
+    <t>Preparacion materiales OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225574303</t>
+  </si>
+  <si>
+    <t>Propuesta MecanizadoOT 4377</t>
+  </si>
+  <si>
+    <t>Generación OC mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>1216769310026493</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT 4377</t>
+  </si>
+  <si>
+    <t>1216774244991438</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser  OT 4377,Fabricacion corte laser OT 4377</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216774111289151</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111289169</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa OT 4377</t>
-  </si>
-  <si>
-    <t>Preparacion materiales OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225574303</t>
-  </si>
-  <si>
-    <t>Propuesta MecanizadoOT 4377</t>
-  </si>
-  <si>
-    <t>Generación OC mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>1216769310026493</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT 4377</t>
-  </si>
-  <si>
-    <t>1216774244991438</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser  OT 4377,Fabricacion corte laser OT 4377</t>
-  </si>
-  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -447,9 +450,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216774225605038</t>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46238.48663269676</v>
+        <v>46239.17839748843</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>65</v>
@@ -2376,7 +2376,7 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="S17" s="12" t="s">
         <v>69</v>
       </c>
       <c r="T17" s="10">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46238.48663290509</v>
+        <v>46239.17839782407</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2439,7 +2439,7 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="7" t="s">
+      <c r="S18" s="12" t="s">
         <v>69</v>
       </c>
       <c r="T18" s="6">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.4866359375</v>
+        <v>46239.17839739584</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>75</v>
@@ -2502,7 +2502,7 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="7" t="s">
+      <c r="S19" s="12" t="s">
         <v>69</v>
       </c>
       <c r="T19" s="10">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46238.48663247685</v>
+        <v>46239.17839734953</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2565,7 +2565,7 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="7" t="s">
+      <c r="S20" s="12" t="s">
         <v>69</v>
       </c>
       <c r="T20" s="6">
@@ -2676,18 +2676,18 @@
         <v>46247</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46225.00941383102</v>
@@ -2697,7 +2697,7 @@
         <v>46225.01069787037</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2730,23 +2730,23 @@
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46225.00942686343</v>
@@ -2756,7 +2756,7 @@
         <v>46225.010714247685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2786,26 +2786,26 @@
         <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46225.00943440972</v>
@@ -2815,7 +2815,7 @@
         <v>46225.01060155092</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2845,7 +2845,7 @@
         <v>81</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2857,18 +2857,18 @@
         <v>46247</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46225.00944026621</v>
@@ -2905,13 +2905,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46225.0094466088</v>
@@ -2931,7 +2931,7 @@
         <v>46225.010798159725</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -2958,13 +2958,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46225.00949415509</v>
@@ -2984,7 +2984,7 @@
         <v>46225.01062606482</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3014,7 +3014,7 @@
         <v>81</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3026,18 +3026,18 @@
         <v>46247</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46225.00950069445</v>
@@ -3074,13 +3074,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46225.00950701389</v>
@@ -3100,7 +3100,7 @@
         <v>46225.01087347222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3127,13 +3127,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="9">
         <v>46225.009512488425</v>
@@ -3153,16 +3153,16 @@
         <v>46225.01064516204</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3183,7 +3183,7 @@
         <v>81</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3195,18 +3195,18 @@
         <v>46247</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3216,16 +3216,16 @@
         <v>46237.55371357639</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3243,13 +3243,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46225.0095310301</v>
@@ -3269,16 +3269,16 @@
         <v>46225.010939224536</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3296,13 +3296,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3322,16 +3322,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3349,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46225.00954297454</v>
@@ -3375,7 +3375,7 @@
         <v>46238.4866103588</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3399,7 +3399,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
@@ -3424,16 +3424,16 @@
         <v>46235.19777150463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3451,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46225.009553993055</v>
@@ -3489,16 +3489,16 @@
         <v>46238.48657123843</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3516,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3531,7 +3531,7 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3581,10 +3581,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>141</v>
@@ -3596,7 +3596,7 @@
         <v>46244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -3644,13 +3644,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3659,13 +3659,13 @@
         <v>46290</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3857,7 +3857,7 @@
         <v>153</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>159</v>
@@ -3869,13 +3869,13 @@
         <v>46260</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3920,7 +3920,7 @@
         <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>162</v>
@@ -3932,13 +3932,13 @@
         <v>46260</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -3983,7 +3983,7 @@
         <v>153</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>165</v>
@@ -3995,13 +3995,13 @@
         <v>46260</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4022,10 +4022,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4058,13 +4058,13 @@
         <v>46261</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4085,10 +4085,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4121,13 +4121,13 @@
         <v>46261</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4148,10 +4148,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4184,13 +4184,13 @@
         <v>46261</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4294,13 +4294,13 @@
         <v>46262</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4357,13 +4357,13 @@
         <v>46267</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4490,10 +4490,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4526,13 +4526,13 @@
         <v>46274</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4553,10 +4553,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4606,10 +4606,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5029,13 +5029,13 @@
         <v>46275</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5198,13 +5198,13 @@
         <v>46286</v>
       </c>
       <c r="S66" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5363,13 +5363,13 @@
         <v>46287</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5532,13 +5532,13 @@
         <v>46288</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5701,13 +5701,13 @@
         <v>46289</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5870,13 +5870,13 @@
         <v>46293</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6086,13 +6086,13 @@
         <v>46294</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6255,13 +6255,13 @@
         <v>46295</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6424,13 +6424,13 @@
         <v>46296</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6593,13 +6593,13 @@
         <v>46297</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6809,13 +6809,13 @@
         <v>46300</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -6872,13 +6872,13 @@
         <v>46300</v>
       </c>
       <c r="S96" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="295">
   <si>
     <t>50001579- "XEMORTIZ C. MEXICANA"</t>
   </si>
@@ -662,121 +662,109 @@
     <t>Montaje Alabe OT 4377 ,Revestimiento OT 4377 ,Montaje motor OT 4377 ,Montaje Rodete OT 4377</t>
   </si>
   <si>
-    <t>1216992723280852</t>
-  </si>
-  <si>
-    <t>Conexión eléctrica OT 4377</t>
+    <t>1216774225731680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774225731703</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Revestimiento OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774111475498</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774205782698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Revestimiento OT 4377 </t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774205782721</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Recepcion Alabe OT 4377 ,Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774245217958</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774245203534</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje motor OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774245203557</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094491864</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225768105</t>
   </si>
   <si>
     <t xml:space="preserve">Montaje motor OT 4377 </t>
   </si>
   <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225770290</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT 4377 ,Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje motor OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774225770419</t>
+  </si>
+  <si>
+    <t>Montaje motor OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774111516366</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pruebas FAT OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774225731680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4377 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774225731703</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Revestimiento OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774111475498</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774205782698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Revestimiento OT 4377 </t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>1216774205782721</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Recepcion Alabe OT 4377 ,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774245217958</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774245203534</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,Montaje motor OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774245203557</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094491864</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225768105</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>Montaje:,Conexión eléctrica OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225770290</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT 4377 ,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Montaje motor OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774225770419</t>
-  </si>
-  <si>
-    <t>Montaje motor OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774111516366</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Conexión eléctrica OT 4377</t>
   </si>
   <si>
     <t>RE-PINTADO OT 4377</t>
@@ -1456,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U96"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -4929,11 +4917,11 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46232.624683587965</v>
+        <v>46225.00993398148</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46232.62478408565</v>
+        <v>46232.6243815625</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -4942,14 +4930,16 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I62" s="5">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="J62" s="5">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -4964,30 +4954,40 @@
         <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="P62" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="Q62" s="5">
+        <v>46281</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46275</v>
+      </c>
+      <c r="S62" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B63" s="9">
-        <v>46225.00993398148</v>
+        <v>46225.00994118056</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46232.6243815625</v>
+        <v>46225.01286980324</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5014,40 +5014,30 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>46281</v>
-      </c>
-      <c r="R63" s="9">
-        <v>46275</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
-        <v>46225.00994118056</v>
+        <v>46225.009955092595</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46225.01286980324</v>
+        <v>46225.01288368055</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>148</v>
@@ -5077,13 +5067,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5093,17 +5083,17 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
-        <v>46225.009955092595</v>
+        <v>46225.00998927084</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46225.01288368055</v>
+        <v>46232.62438284722</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5115,10 +5105,10 @@
         <v>55</v>
       </c>
       <c r="I65" s="9">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="J65" s="9">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>26</v>
@@ -5130,33 +5120,43 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+      <c r="Q65" s="9">
+        <v>46286</v>
+      </c>
+      <c r="R65" s="9">
+        <v>46286</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T65" s="10">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>219</v>
       </c>
       <c r="B66" s="5">
-        <v>46225.00998927084</v>
+        <v>46225.00999641204</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46232.62438284722</v>
+        <v>46238.48662206018</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5167,9 +5167,7 @@
       <c r="H66" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I66" s="5">
-        <v>46286</v>
-      </c>
+      <c r="I66" s="6"/>
       <c r="J66" s="5">
         <v>46286</v>
       </c>
@@ -5183,40 +5181,30 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="P66" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>46286</v>
-      </c>
-      <c r="R66" s="5">
-        <v>46286</v>
-      </c>
-      <c r="S66" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B67" s="9">
-        <v>46225.00999641204</v>
+        <v>46225.01000505787</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46238.48662206018</v>
+        <v>46238.48661143519</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>148</v>
@@ -5244,13 +5232,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O67" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="O67" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5260,17 +5248,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
-        <v>46225.01000505787</v>
+        <v>46225.010088842595</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46238.48661143519</v>
+        <v>46232.624382546295</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5281,9 +5269,11 @@
       <c r="H68" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I68" s="6"/>
+      <c r="I68" s="5">
+        <v>46287</v>
+      </c>
       <c r="J68" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5295,33 +5285,43 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="Q68" s="5">
+        <v>46287</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>228</v>
       </c>
       <c r="B69" s="9">
-        <v>46225.010088842595</v>
+        <v>46225.01009811343</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46232.624382546295</v>
+        <v>46225.01320763888</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5348,40 +5348,30 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="P69" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q69" s="9">
-        <v>46287</v>
-      </c>
-      <c r="R69" s="9">
-        <v>46287</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B70" s="5">
-        <v>46225.01009811343</v>
+        <v>46225.0101059838</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.01320763888</v>
+        <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>148</v>
@@ -5411,13 +5401,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="O70" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="O70" s="6" t="s">
-        <v>233</v>
-      </c>
       <c r="P70" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5427,17 +5417,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B71" s="9">
-        <v>46225.0101059838</v>
+        <v>46225.01014195602</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46225.013223182876</v>
+        <v>46240.82233700232</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5449,10 +5439,10 @@
         <v>55</v>
       </c>
       <c r="I71" s="9">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="J71" s="9">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
@@ -5464,33 +5454,43 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="10"/>
-      <c r="T71" s="10"/>
-      <c r="U71" s="10"/>
+        <v>206</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>46288</v>
+      </c>
+      <c r="R71" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T71" s="10">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46225.01014195602</v>
+        <v>46225.01015462963</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46232.62478408565</v>
+        <v>46238.486621041666</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5517,40 +5517,30 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P72" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46288</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B73" s="9">
-        <v>46225.01015462963</v>
+        <v>46225.01016259259</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46238.486621041666</v>
+        <v>46238.4866215625</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>148</v>
@@ -5580,13 +5570,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5596,17 +5586,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
-        <v>46225.01016259259</v>
+        <v>46225.01019770833</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46238.4866215625</v>
+        <v>46240.82233707176</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5618,10 +5608,10 @@
         <v>55</v>
       </c>
       <c r="I74" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="J74" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5633,33 +5623,43 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+        <v>243</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46289</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46289</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T74" s="6">
+        <v>0</v>
+      </c>
+      <c r="U74" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
-        <v>46225.01019770833</v>
+        <v>46225.010204872684</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46232.624783935185</v>
+        <v>46225.013478761575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5671,10 +5671,10 @@
         <v>55</v>
       </c>
       <c r="I75" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="J75" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
@@ -5686,40 +5686,30 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="P75" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>46289</v>
-      </c>
-      <c r="R75" s="9">
-        <v>46289</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46225.010204872684</v>
+        <v>46225.01021453703</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.013478761575</v>
+        <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>148</v>
@@ -5749,13 +5739,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5765,17 +5755,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
-        <v>46225.01021453703</v>
+        <v>46225.0103003125</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46225.01351359954</v>
+        <v>46232.624382152775</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5787,10 +5777,10 @@
         <v>55</v>
       </c>
       <c r="I77" s="9">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="J77" s="9">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5802,33 +5792,43 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46293</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46225.0103003125</v>
+        <v>46225.01030866898</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46232.624382152775</v>
+        <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>247</v>
+        <v>148</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5855,40 +5855,30 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>148</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>46293</v>
-      </c>
-      <c r="R78" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S78" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46225.01030866898</v>
+        <v>46225.010315949075</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46225.0136440625</v>
+        <v>46225.01367180556</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>148</v>
@@ -5918,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>148</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5934,33 +5924,27 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46225.010315949075</v>
+        <v>46225.010349062504</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.01367180556</v>
+        <v>46225.010597650464</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46293</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46293</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
       <c r="K80" s="6" t="s">
         <v>26</v>
       </c>
@@ -5968,16 +5952,16 @@
         <v>26</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5987,27 +5971,33 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
-        <v>46225.010349062504</v>
+        <v>46225.010352893514</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.010597650464</v>
+        <v>46225.58761383102</v>
       </c>
       <c r="E81" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F81" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
+      <c r="H81" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I81" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J81" s="9">
+        <v>46294</v>
+      </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
       </c>
@@ -6015,45 +6005,55 @@
         <v>26</v>
       </c>
       <c r="M81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="O81" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T81" s="10">
         <v>0</v>
       </c>
-      <c r="N81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O81" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+      <c r="U81" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46225.010352893514</v>
+        <v>46225.010361319444</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.58761383102</v>
+        <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I82" s="5">
         <v>46294</v>
@@ -6071,40 +6071,30 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46294</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46294</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46225.010361319444</v>
+        <v>46225.0103680787</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46225.01378356482</v>
+        <v>46225.01379511574</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>148</v>
@@ -6113,10 +6103,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I83" s="9">
         <v>46294</v>
@@ -6134,13 +6124,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>148</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6150,32 +6140,32 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46225.0103680787</v>
+        <v>46225.010400983796</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46225.01379511574</v>
+        <v>46225.587646631946</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>263</v>
+        <v>54</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>264</v>
+        <v>55</v>
       </c>
       <c r="I84" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="J84" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6187,33 +6177,43 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>148</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46295</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46295</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
-        <v>46225.010400983796</v>
+        <v>46225.010407800924</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46225.587646631946</v>
+        <v>46225.013919687495</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>271</v>
+        <v>148</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6240,40 +6240,30 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>272</v>
+        <v>148</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>46295</v>
-      </c>
-      <c r="R85" s="9">
-        <v>46295</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46225.010407800924</v>
+        <v>46225.010414502314</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46225.013919687495</v>
+        <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>148</v>
@@ -6303,13 +6293,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6319,32 +6309,32 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46225.010414502314</v>
+        <v>46225.01048866898</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46225.013935787036</v>
+        <v>46225.58766351852</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="I87" s="9">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J87" s="9">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6356,33 +6346,43 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+        <v>255</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>46296</v>
+      </c>
+      <c r="R87" s="9">
+        <v>46296</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T87" s="10">
+        <v>0</v>
+      </c>
+      <c r="U87" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46225.01048866898</v>
+        <v>46225.01049565972</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46225.58766351852</v>
+        <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>278</v>
+        <v>148</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6409,40 +6409,30 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46296</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46296</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46225.01049565972</v>
+        <v>46225.01050163194</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46225.014048425925</v>
+        <v>46225.014061504626</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>148</v>
@@ -6472,13 +6462,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>148</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6488,17 +6478,17 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46225.01050163194</v>
+        <v>46225.01053885417</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46225.014061504626</v>
+        <v>46225.587682592595</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6510,10 +6500,10 @@
         <v>179</v>
       </c>
       <c r="I90" s="5">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J90" s="5">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -6525,33 +6515,43 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+      <c r="Q90" s="5">
+        <v>46297</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46297</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0</v>
+      </c>
+      <c r="U90" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46225.01053885417</v>
+        <v>46225.01054688657</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46225.587682592595</v>
+        <v>46225.014210312496</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6578,40 +6578,30 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q91" s="9">
-        <v>46297</v>
-      </c>
-      <c r="R91" s="9">
-        <v>46297</v>
-      </c>
-      <c r="S91" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T91" s="10">
-        <v>0</v>
-      </c>
-      <c r="U91" s="11" t="s">
-        <v>88</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46225.01054688657</v>
+        <v>46225.010553252316</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46225.014210312496</v>
+        <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>148</v>
@@ -6641,13 +6631,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6657,33 +6647,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46225.010553252316</v>
+        <v>46225.010582800925</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46225.01422244213</v>
+        <v>46225.010649097225</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I93" s="9">
-        <v>46297</v>
-      </c>
-      <c r="J93" s="9">
-        <v>46297</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
         <v>26</v>
       </c>
@@ -6691,16 +6675,16 @@
         <v>26</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>283</v>
+        <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>148</v>
+        <v>287</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>26</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6710,27 +6694,33 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
-        <v>46225.010582800925</v>
+        <v>46225.01058614583</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46225.010649097225</v>
+        <v>46225.01625800926</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+      <c r="H94" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46300</v>
+      </c>
+      <c r="J94" s="5">
+        <v>46304</v>
+      </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -6738,45 +6728,55 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="N94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="11" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B95" s="9">
-        <v>46225.01058614583</v>
+        <v>46225.01062565972</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46225.01625800926</v>
+        <v>46225.01625788194</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>294</v>
+        <v>30</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>295</v>
+        <v>31</v>
       </c>
       <c r="I95" s="9">
         <v>46300</v>
@@ -6794,13 +6794,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="9">
         <v>46304</v>
@@ -6815,69 +6815,6 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B96" s="5">
-        <v>46225.01062565972</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="5">
-        <v>46225.01625788194</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46300</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46304</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46300</v>
-      </c>
-      <c r="S96" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="11" t="s">
         <v>88</v>
       </c>
     </row>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3474,7 +3474,7 @@
         <v>46238.486553622686</v>
       </c>
       <c r="D37" s="9">
-        <v>46238.48657123843</v>
+        <v>46242.19777017361</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>136</v>
@@ -3518,8 +3518,8 @@
       <c r="R37" s="9">
         <v>46237</v>
       </c>
-      <c r="S37" s="12" t="s">
-        <v>69</v>
+      <c r="S37" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="294">
   <si>
     <t>50001579- "XEMORTIZ C. MEXICANA"</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC corte laser  OT 4377</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -2320,7 +2317,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.250874143516</v>
+        <v>46247.186268969905</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>65</v>
@@ -2364,29 +2361,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>69</v>
+      <c r="S17" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5">
         <v>46225.009388923616</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46246.25087695602</v>
+        <v>46247.186269375</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2419,7 +2416,7 @@
         <v>67</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2427,29 +2424,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>69</v>
+      <c r="S18" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="9">
         <v>46225.009394699075</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46246.25087832176</v>
+        <v>46247.186269074075</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2482,7 +2479,7 @@
         <v>67</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2490,29 +2487,29 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>69</v>
+      <c r="S19" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5">
         <v>46225.00940033565</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46246.250879687504</v>
+        <v>46247.186268923615</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2545,7 +2542,7 @@
         <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2553,19 +2550,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>69</v>
+      <c r="S20" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="9">
         <v>46225.00920047454</v>
@@ -2575,7 +2572,7 @@
         <v>46225.00964425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2599,7 +2596,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2612,7 +2609,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="5">
         <v>46225.00940686342</v>
@@ -2622,16 +2619,16 @@
         <v>46225.01056048612</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2649,13 +2646,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2664,18 +2661,18 @@
         <v>46247</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9">
         <v>46225.00941383102</v>
@@ -2685,16 +2682,16 @@
         <v>46225.01069787037</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I23" s="9">
         <v>46247</v>
@@ -2712,29 +2709,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46225.00942686343</v>
@@ -2744,16 +2741,16 @@
         <v>46225.010714247685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2771,29 +2768,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46225.00943440972</v>
@@ -2803,16 +2800,16 @@
         <v>46225.01060155092</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -2830,10 +2827,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2845,18 +2842,18 @@
         <v>46247</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46225.00944026621</v>
@@ -2866,16 +2863,16 @@
         <v>46225.010778923606</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -2893,13 +2890,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2909,7 +2906,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46225.0094466088</v>
@@ -2919,16 +2916,16 @@
         <v>46225.010798159725</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I27" s="9">
         <v>46251</v>
@@ -2946,13 +2943,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -2962,7 +2959,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46225.00949415509</v>
@@ -2972,16 +2969,16 @@
         <v>46225.01062606482</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -2999,10 +2996,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3014,18 +3011,18 @@
         <v>46247</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46225.00950069445</v>
@@ -3035,16 +3032,16 @@
         <v>46225.01085252315</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I29" s="9">
         <v>46247</v>
@@ -3062,13 +3059,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3078,7 +3075,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46225.00950701389</v>
@@ -3088,16 +3085,16 @@
         <v>46225.01087347222</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3115,13 +3112,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3131,7 +3128,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="9">
         <v>46225.009512488425</v>
@@ -3141,16 +3138,16 @@
         <v>46225.01064516204</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3168,10 +3165,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3183,18 +3180,18 @@
         <v>46247</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3204,16 +3201,16 @@
         <v>46237.55371357639</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3231,13 +3228,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3247,7 +3244,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46225.0095310301</v>
@@ -3257,16 +3254,16 @@
         <v>46225.010939224536</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3284,13 +3281,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3300,7 +3297,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3310,16 +3307,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3337,13 +3334,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3353,7 +3350,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46225.00954297454</v>
@@ -3363,7 +3360,7 @@
         <v>46238.4866103588</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3387,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3400,7 +3397,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
@@ -3412,16 +3409,16 @@
         <v>46235.19777150463</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3439,13 +3436,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3465,7 +3462,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46225.009553993055</v>
@@ -3477,16 +3474,16 @@
         <v>46242.19777017361</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3504,13 +3501,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3530,7 +3527,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46225.00956064815</v>
@@ -3548,10 +3545,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3569,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3595,7 +3592,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="9">
         <v>46225.00957443287</v>
@@ -3605,16 +3602,16 @@
         <v>46225.01576019676</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3632,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3647,18 +3644,18 @@
         <v>46290</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3668,16 +3665,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3693,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3709,7 +3706,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46225.00958684028</v>
@@ -3719,16 +3716,16 @@
         <v>46225.01157688657</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3744,13 +3741,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3760,7 +3757,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3770,7 +3767,7 @@
         <v>46225.009844733795</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3794,7 +3791,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3807,7 +3804,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46225.00968099537</v>
@@ -3817,16 +3814,16 @@
         <v>46225.011108125</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -3842,13 +3839,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3857,18 +3854,18 @@
         <v>46260</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
@@ -3878,16 +3875,16 @@
         <v>46225.01115158565</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3905,13 +3902,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3920,18 +3917,18 @@
         <v>46260</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46225.00969839121</v>
@@ -3941,16 +3938,16 @@
         <v>46225.011180127316</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3968,13 +3965,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -3983,18 +3980,18 @@
         <v>46260</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
@@ -4004,16 +4001,16 @@
         <v>46225.01480951389</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4031,13 +4028,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4046,18 +4043,18 @@
         <v>46261</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="9">
         <v>46225.00971478009</v>
@@ -4067,16 +4064,16 @@
         <v>46225.01480953704</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4094,13 +4091,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4109,18 +4106,18 @@
         <v>46261</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
@@ -4130,16 +4127,16 @@
         <v>46225.0148096412</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4157,13 +4154,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4172,18 +4169,18 @@
         <v>46261</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46225.00973607639</v>
@@ -4193,7 +4190,7 @@
         <v>46225.00984827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4217,7 +4214,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4230,7 +4227,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4240,16 +4237,16 @@
         <v>46225.01481001158</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4267,13 +4264,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4282,18 +4279,18 @@
         <v>46262</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B51" s="9">
         <v>46225.00974854166</v>
@@ -4303,16 +4300,16 @@
         <v>46225.01480996527</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4330,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4345,18 +4342,18 @@
         <v>46267</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4366,16 +4363,16 @@
         <v>46238.486620069445</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4393,13 +4390,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4409,7 +4406,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="9">
         <v>46225.00976584491</v>
@@ -4419,16 +4416,16 @@
         <v>46238.48661083334</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4446,13 +4443,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4462,7 +4459,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
@@ -4472,16 +4469,16 @@
         <v>46225.01496555556</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4499,13 +4496,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -4514,18 +4511,18 @@
         <v>46274</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="9">
         <v>46225.00981328703</v>
@@ -4535,16 +4532,16 @@
         <v>46238.48662065972</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4562,13 +4559,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4578,7 +4575,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4588,16 +4585,16 @@
         <v>46238.48661202546</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4615,13 +4612,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4631,7 +4628,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46225.00990130787</v>
@@ -4641,7 +4638,7 @@
         <v>46225.010049375</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4665,7 +4662,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4678,7 +4675,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
@@ -4688,16 +4685,16 @@
         <v>46232.1720309375</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4715,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4736,12 +4733,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46225.00991375</v>
@@ -4751,16 +4748,16 @@
         <v>46232.172030752314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I59" s="9">
         <v>46230</v>
@@ -4778,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="9">
         <v>46231</v>
@@ -4799,12 +4796,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
@@ -4814,16 +4811,16 @@
         <v>46232.17203079861</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4841,13 +4838,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4862,12 +4859,12 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46225.009930162036</v>
@@ -4877,7 +4874,7 @@
         <v>46232.62468724537</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -4901,7 +4898,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -4914,7 +4911,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46225.00993398148</v>
@@ -4924,7 +4921,7 @@
         <v>46232.6243815625</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4951,13 +4948,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q62" s="5">
         <v>46281</v>
@@ -4966,18 +4963,18 @@
         <v>46275</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46225.00994118056</v>
@@ -4987,7 +4984,7 @@
         <v>46225.01286980324</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5014,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5030,7 +5027,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" s="5">
         <v>46225.009955092595</v>
@@ -5040,7 +5037,7 @@
         <v>46225.01288368055</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5067,13 +5064,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5083,7 +5080,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" s="9">
         <v>46225.00998927084</v>
@@ -5093,7 +5090,7 @@
         <v>46232.62438284722</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5120,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="Q65" s="9">
         <v>46286</v>
@@ -5135,18 +5132,18 @@
         <v>46286</v>
       </c>
       <c r="S65" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46225.00999641204</v>
@@ -5156,7 +5153,7 @@
         <v>46238.48662206018</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5181,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5197,7 +5194,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B67" s="9">
         <v>46225.01000505787</v>
@@ -5207,7 +5204,7 @@
         <v>46238.48661143519</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5232,13 +5229,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5248,7 +5245,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
         <v>46225.010088842595</v>
@@ -5258,7 +5255,7 @@
         <v>46232.624382546295</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5285,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q68" s="5">
         <v>46287</v>
@@ -5300,18 +5297,18 @@
         <v>46287</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="9">
         <v>46225.01009811343</v>
@@ -5321,7 +5318,7 @@
         <v>46225.01320763888</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5348,13 +5345,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5364,7 +5361,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46225.0101059838</v>
@@ -5374,7 +5371,7 @@
         <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5401,13 +5398,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5417,7 +5414,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B71" s="9">
         <v>46225.01014195602</v>
@@ -5427,7 +5424,7 @@
         <v>46240.82233700232</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5454,13 +5451,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q71" s="9">
         <v>46288</v>
@@ -5469,18 +5466,18 @@
         <v>46288</v>
       </c>
       <c r="S71" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46225.01015462963</v>
@@ -5490,7 +5487,7 @@
         <v>46238.486621041666</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5517,13 +5514,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5533,7 +5530,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46225.01016259259</v>
@@ -5543,7 +5540,7 @@
         <v>46238.4866215625</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5570,13 +5567,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5586,7 +5583,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46225.01019770833</v>
@@ -5596,7 +5593,7 @@
         <v>46240.82233707176</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5623,13 +5620,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="5">
         <v>46289</v>
@@ -5638,18 +5635,18 @@
         <v>46289</v>
       </c>
       <c r="S74" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46225.010204872684</v>
@@ -5659,7 +5656,7 @@
         <v>46225.013478761575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5686,13 +5683,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5702,7 +5699,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46225.01021453703</v>
@@ -5712,7 +5709,7 @@
         <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5739,13 +5736,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5755,7 +5752,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46225.0103003125</v>
@@ -5765,7 +5762,7 @@
         <v>46232.624382152775</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5792,10 +5789,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -5807,18 +5804,18 @@
         <v>46293</v>
       </c>
       <c r="S77" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46225.01030866898</v>
@@ -5828,7 +5825,7 @@
         <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5855,13 +5852,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5871,7 +5868,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46225.010315949075</v>
@@ -5881,7 +5878,7 @@
         <v>46225.01367180556</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5908,13 +5905,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5924,7 +5921,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46225.010349062504</v>
@@ -5934,7 +5931,7 @@
         <v>46225.010597650464</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -5958,7 +5955,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -5971,7 +5968,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B81" s="9">
         <v>46225.010352893514</v>
@@ -5981,16 +5978,16 @@
         <v>46225.58761383102</v>
       </c>
       <c r="E81" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="F81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="H81" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>260</v>
       </c>
       <c r="I81" s="9">
         <v>46294</v>
@@ -6008,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="9">
         <v>46294</v>
@@ -6023,18 +6020,18 @@
         <v>46294</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46225.010361319444</v>
@@ -6044,16 +6041,16 @@
         <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="I82" s="5">
         <v>46294</v>
@@ -6071,13 +6068,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6087,7 +6084,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46225.0103680787</v>
@@ -6097,16 +6094,16 @@
         <v>46225.01379511574</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>260</v>
       </c>
       <c r="I83" s="9">
         <v>46294</v>
@@ -6124,13 +6121,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46225.010400983796</v>
@@ -6150,7 +6147,7 @@
         <v>46225.587646631946</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6177,10 +6174,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6192,18 +6189,18 @@
         <v>46295</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46225.010407800924</v>
@@ -6213,7 +6210,7 @@
         <v>46225.013919687495</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6240,13 +6237,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6256,7 +6253,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46225.010414502314</v>
@@ -6266,7 +6263,7 @@
         <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6293,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46225.01048866898</v>
@@ -6319,16 +6316,16 @@
         <v>46225.58766351852</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I87" s="9">
         <v>46296</v>
@@ -6346,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q87" s="9">
         <v>46296</v>
@@ -6361,18 +6358,18 @@
         <v>46296</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46225.01049565972</v>
@@ -6382,16 +6379,16 @@
         <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6409,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6425,7 +6422,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46225.01050163194</v>
@@ -6435,16 +6432,16 @@
         <v>46225.014061504626</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I89" s="9">
         <v>46296</v>
@@ -6462,13 +6459,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6478,7 +6475,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46225.01053885417</v>
@@ -6488,16 +6485,16 @@
         <v>46225.587682592595</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I90" s="5">
         <v>46297</v>
@@ -6515,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q90" s="5">
         <v>46297</v>
@@ -6530,18 +6527,18 @@
         <v>46297</v>
       </c>
       <c r="S90" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46225.01054688657</v>
@@ -6551,16 +6548,16 @@
         <v>46225.014210312496</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I91" s="9">
         <v>46297</v>
@@ -6578,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6594,7 +6591,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46225.010553252316</v>
@@ -6604,16 +6601,16 @@
         <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>
@@ -6631,13 +6628,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6647,7 +6644,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B93" s="9">
         <v>46225.010582800925</v>
@@ -6657,7 +6654,7 @@
         <v>46225.010649097225</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6681,7 +6678,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B94" s="5">
         <v>46225.01058614583</v>
@@ -6704,16 +6701,16 @@
         <v>46225.01625800926</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="I94" s="5">
         <v>46300</v>
@@ -6731,13 +6728,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q94" s="5">
         <v>46304</v>
@@ -6746,18 +6743,18 @@
         <v>46300</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B95" s="9">
         <v>46225.01062565972</v>
@@ -6767,7 +6764,7 @@
         <v>46225.01625788194</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6794,13 +6791,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="9">
         <v>46304</v>
@@ -6809,13 +6806,13 @@
         <v>46300</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46225.01069787037</v>
+        <v>46248.17135199074</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>89</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46225.010778923606</v>
+        <v>46248.171349421296</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>72</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46225.01085252315</v>
+        <v>46248.17135076389</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>78</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46225.011108125</v>
+        <v>46253.19684533565</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>156</v>
@@ -3856,8 +3856,8 @@
       <c r="R43" s="9">
         <v>46260</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>91</v>
+      <c r="S43" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46225.01115158565</v>
+        <v>46253.19684528935</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>161</v>
@@ -3919,8 +3919,8 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>91</v>
+      <c r="S44" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46225.011180127316</v>
+        <v>46253.196845185186</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>164</v>
@@ -3982,8 +3982,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>91</v>
+      <c r="S45" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46225.01480951389</v>
+        <v>46254.16881054398</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>167</v>
@@ -4045,8 +4045,8 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>91</v>
+      <c r="S46" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46225.01480953704</v>
+        <v>46254.16881052083</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>170</v>
@@ -4108,8 +4108,8 @@
       <c r="R47" s="9">
         <v>46261</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>91</v>
+      <c r="S47" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46225.0148096412</v>
+        <v>46254.168810902775</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -4171,8 +4171,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>91</v>
+      <c r="S48" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -392,7 +392,7 @@
     <t>Generacion Oc  OT 4377</t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t>Fabricación externa  OT 4377,Armado OT 4377</t>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46237.55371357639</v>
+        <v>46254.64730739583</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46254.64730739583</v>
+        <v>46255.17031515046</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46255.17031515046</v>
+        <v>46255.62865266204</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46252.17548762732</v>
+        <v>46259.16928217592</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>81</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46225.010714247685</v>
+        <v>46259.16928101852</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46252.17548767361</v>
+        <v>46259.16928390047</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>96</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46225.010798159725</v>
+        <v>46259.16930353009</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>101</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46252.17548762732</v>
+        <v>46259.16930430556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>104</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46225.01087347222</v>
+        <v>46259.1692796875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46225.01481001158</v>
+        <v>46259.17901423611</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>75</v>
@@ -4281,8 +4281,8 @@
       <c r="R50" s="5">
         <v>46262</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>91</v>
+      <c r="S50" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -296,226 +296,226 @@
     <t>Generación OC corte laser  OT 4377,Fabricacion corte laser OT 4377</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216774244991461</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser  OT 4377</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT 4377,Fabricacion corte laser OT 4377</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1216774225576653</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser OT 4377</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT 4377,Recepcion corte laser OT 4377</t>
+  </si>
+  <si>
+    <t>1216774245016310</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma  OT 4377,Fabricación corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>1216774094332857</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4377,Fabricación corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>1216774094332880</t>
+  </si>
+  <si>
+    <t>Fabricación corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4377,Recepcion corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t>1216786922451562</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4377,Generación OC mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774205653712</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4377,Mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774094346169</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4377,Recepcion mecanizadoOT 4377</t>
+  </si>
+  <si>
+    <t>1216774094346192</t>
+  </si>
+  <si>
+    <t>Fabricación externa  OT 4377</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT 4377,Generacion Oc  OT 4377,Armado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111322476</t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t>Fabricación externa  OT 4377,Armado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774245068729</t>
+  </si>
+  <si>
+    <t>Armado OT 4377</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT 4377,Fabricación externa  OT 4377</t>
+  </si>
+  <si>
+    <t>1216774245068752</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT 4377</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216774094354676</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4377,Check pruebas FAT OT 4377,Plano Preliminar OT 4377,Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111324768</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT 4377</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111324796</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT 4377</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225605038</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Propuesta Fabricación externa OT 4377,Propuesta MecanizadoOT 4377,Propuesta Corte plasma  OT 4377,propuesta Corte laserOT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094355990</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT 4377</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094363252</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094363270</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT OT 4377,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774245083506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4377,Recepcion corte plasma  OT 4377,Recepcion mecanizadoOT 4377,Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Recepcion corte laser OT 4377</t>
+  </si>
+  <si>
+    <t>1216774094355966</t>
+  </si>
+  <si>
+    <t>Recepcion corte laser OT 4377</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte LaserOT 4377,Bodega </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216774244991461</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser  OT 4377</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT 4377,Fabricacion corte laser OT 4377</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1216774225576653</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser OT 4377</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT 4377,Recepcion corte laser OT 4377</t>
-  </si>
-  <si>
-    <t>1216774245016310</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma  OT 4377,Fabricación corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>1216774094332857</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4377,Fabricación corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>1216774094332880</t>
-  </si>
-  <si>
-    <t>Fabricación corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4377,Recepcion corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t>1216786922451562</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4377,Generación OC mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774205653712</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4377,Mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774094346169</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4377,Recepcion mecanizadoOT 4377</t>
-  </si>
-  <si>
-    <t>1216774094346192</t>
-  </si>
-  <si>
-    <t>Fabricación externa  OT 4377</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT 4377,Generacion Oc  OT 4377,Armado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111322476</t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t>Fabricación externa  OT 4377,Armado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774245068729</t>
-  </si>
-  <si>
-    <t>Armado OT 4377</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT 4377,Fabricación externa  OT 4377</t>
-  </si>
-  <si>
-    <t>1216774245068752</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT 4377</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216774094354676</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4377,Check pruebas FAT OT 4377,Plano Preliminar OT 4377,Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111324768</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT 4377</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111324796</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT 4377</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225605038</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Propuesta Fabricación externa OT 4377,Propuesta MecanizadoOT 4377,Propuesta Corte plasma  OT 4377,propuesta Corte laserOT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094355990</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT 4377</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094363252</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT 4377,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094363270</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT OT 4377,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774245083506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4377,Recepcion corte plasma  OT 4377,Recepcion mecanizadoOT 4377,Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Recepcion corte laser OT 4377</t>
-  </si>
-  <si>
-    <t>1216774094355966</t>
-  </si>
-  <si>
-    <t>Recepcion corte laser OT 4377</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte LaserOT 4377,Bodega </t>
   </si>
   <si>
     <t>1216774245125184</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46259.16928217592</v>
+        <v>46260.16792832176</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>81</v>
@@ -2663,19 +2663,19 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>86</v>
+      <c r="S22" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="9">
         <v>46225.00941383102</v>
@@ -2685,7 +2685,7 @@
         <v>46248.17135199074</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2718,23 +2718,23 @@
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46225.00942686343</v>
@@ -2744,7 +2744,7 @@
         <v>46259.16928101852</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2774,36 +2774,36 @@
         <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46225.00943440972</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46259.16928390047</v>
+        <v>46260.167928518524</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2833,7 +2833,7 @@
         <v>80</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2844,19 +2844,19 @@
       <c r="R25" s="9">
         <v>46247</v>
       </c>
-      <c r="S25" s="12" t="s">
-        <v>86</v>
+      <c r="S25" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46225.00944026621</v>
@@ -2893,13 +2893,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46225.0094466088</v>
@@ -2919,7 +2919,7 @@
         <v>46259.16930353009</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -2946,13 +2946,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -2962,17 +2962,17 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46225.00949415509</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46259.16930430556</v>
+        <v>46260.16792878472</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3002,7 +3002,7 @@
         <v>80</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3013,19 +3013,19 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>86</v>
+      <c r="S28" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46225.00950069445</v>
@@ -3062,13 +3062,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46225.00950701389</v>
@@ -3088,7 +3088,7 @@
         <v>46259.1692796875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3115,13 +3115,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="9">
         <v>46225.009512488425</v>
@@ -3141,16 +3141,16 @@
         <v>46225.01064516204</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3171,7 +3171,7 @@
         <v>80</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3183,18 +3183,18 @@
         <v>46247</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3204,16 +3204,16 @@
         <v>46255.62865266204</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3231,13 +3231,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46225.0095310301</v>
@@ -3257,16 +3257,16 @@
         <v>46225.010939224536</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3284,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3310,16 +3310,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3337,13 +3337,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46225.00954297454</v>
@@ -3363,7 +3363,7 @@
         <v>46238.4866103588</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3387,7 +3387,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
@@ -3412,16 +3412,16 @@
         <v>46235.19777150463</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3439,13 +3439,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46225.009553993055</v>
@@ -3477,16 +3477,16 @@
         <v>46242.19777017361</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3504,13 +3504,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46225.00956064815</v>
@@ -3548,10 +3548,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3569,13 +3569,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="9">
         <v>46225.00957443287</v>
@@ -3605,16 +3605,16 @@
         <v>46225.01576019676</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3632,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3647,18 +3647,18 @@
         <v>46290</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3668,16 +3668,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3693,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46225.00958684028</v>
@@ -3719,16 +3719,16 @@
         <v>46225.01157688657</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3770,7 +3770,7 @@
         <v>46225.009844733795</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3807,26 +3807,26 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46225.00968099537</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46253.19684533565</v>
+        <v>46260.16929189815</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -3842,13 +3842,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3857,13 +3857,13 @@
         <v>46260</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46253.19684528935</v>
+        <v>46260.169295162035</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>161</v>
@@ -3884,10 +3884,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3905,10 +3905,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>162</v>
@@ -3920,13 +3920,13 @@
         <v>46260</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46253.196845185186</v>
+        <v>46260.1692934375</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>164</v>
@@ -3947,10 +3947,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3968,10 +3968,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>165</v>
@@ -3983,13 +3983,13 @@
         <v>46260</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4031,10 +4031,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>168</v>
@@ -4046,13 +4046,13 @@
         <v>46261</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4073,10 +4073,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4094,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>161</v>
@@ -4109,13 +4109,13 @@
         <v>46261</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4136,10 +4136,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4157,7 +4157,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>164</v>
@@ -4172,13 +4172,13 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4282,13 +4282,13 @@
         <v>46262</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>175</v>
@@ -4345,13 +4345,13 @@
         <v>46267</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4366,7 +4366,7 @@
         <v>46238.486620069445</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4419,7 +4419,7 @@
         <v>46238.48661083334</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4478,10 +4478,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4502,7 +4502,7 @@
         <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>175</v>
@@ -4514,13 +4514,13 @@
         <v>46274</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4535,16 +4535,16 @@
         <v>46238.48662065972</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4588,16 +4588,16 @@
         <v>46238.48661202546</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4694,10 +4694,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4757,10 +4757,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I59" s="9">
         <v>46230</v>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4820,10 +4820,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4954,7 +4954,7 @@
         <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>210</v>
@@ -4966,13 +4966,13 @@
         <v>46275</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -4987,7 +4987,7 @@
         <v>46225.01286980324</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5017,7 +5017,7 @@
         <v>209</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>212</v>
@@ -5040,7 +5040,7 @@
         <v>46225.01288368055</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5070,7 +5070,7 @@
         <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>214</v>
@@ -5135,13 +5135,13 @@
         <v>46286</v>
       </c>
       <c r="S65" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5156,7 +5156,7 @@
         <v>46238.48662206018</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5207,7 +5207,7 @@
         <v>46238.48661143519</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5300,13 +5300,13 @@
         <v>46287</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5321,7 +5321,7 @@
         <v>46225.01320763888</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5374,7 +5374,7 @@
         <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5469,13 +5469,13 @@
         <v>46288</v>
       </c>
       <c r="S71" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5490,7 +5490,7 @@
         <v>46238.486621041666</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5543,7 +5543,7 @@
         <v>46238.4866215625</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5626,7 +5626,7 @@
         <v>206</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>243</v>
@@ -5638,13 +5638,13 @@
         <v>46289</v>
       </c>
       <c r="S74" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5659,7 +5659,7 @@
         <v>46225.013478761575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5712,7 +5712,7 @@
         <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5807,13 +5807,13 @@
         <v>46293</v>
       </c>
       <c r="S77" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
         <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5858,7 +5858,7 @@
         <v>243</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>251</v>
@@ -5881,7 +5881,7 @@
         <v>46225.01367180556</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5911,7 +5911,7 @@
         <v>243</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>253</v>
@@ -6011,7 +6011,7 @@
         <v>255</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>261</v>
@@ -6023,13 +6023,13 @@
         <v>46294</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6044,7 +6044,7 @@
         <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6074,7 +6074,7 @@
         <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>263</v>
@@ -6097,7 +6097,7 @@
         <v>46225.01379511574</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6127,7 +6127,7 @@
         <v>258</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>265</v>
@@ -6192,13 +6192,13 @@
         <v>46295</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6213,7 +6213,7 @@
         <v>46225.013919687495</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6243,7 +6243,7 @@
         <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>270</v>
@@ -6266,7 +6266,7 @@
         <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6296,7 +6296,7 @@
         <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>272</v>
@@ -6349,7 +6349,7 @@
         <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>255</v>
@@ -6361,13 +6361,13 @@
         <v>46296</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6382,7 +6382,7 @@
         <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6412,7 +6412,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>276</v>
@@ -6435,7 +6435,7 @@
         <v>46225.014061504626</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6465,7 +6465,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6518,7 +6518,7 @@
         <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>280</v>
@@ -6530,13 +6530,13 @@
         <v>46297</v>
       </c>
       <c r="S90" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -6551,7 +6551,7 @@
         <v>46225.014210312496</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6581,7 +6581,7 @@
         <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>282</v>
@@ -6604,7 +6604,7 @@
         <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6634,7 +6634,7 @@
         <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>284</v>
@@ -6746,13 +6746,13 @@
         <v>46300</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6809,13 +6809,13 @@
         <v>46300</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -515,34 +515,34 @@
     <t xml:space="preserve">Control de calidad corte LaserOT 4377,Bodega </t>
   </si>
   <si>
+    <t>1216774245125184</t>
+  </si>
+  <si>
+    <t>Recepcion corte plasma  OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma OT 4377,Bodega </t>
+  </si>
+  <si>
+    <t>1216774111387793</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizadoOT 4377</t>
+  </si>
+  <si>
+    <t>Bodega ,Control de calidad Mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225627302</t>
+  </si>
+  <si>
+    <t>Control de calidad corte LaserOT 4377</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Bodega ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774245125184</t>
-  </si>
-  <si>
-    <t>Recepcion corte plasma  OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma OT 4377,Bodega </t>
-  </si>
-  <si>
-    <t>1216774111387793</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizadoOT 4377</t>
-  </si>
-  <si>
-    <t>Bodega ,Control de calidad Mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225627302</t>
-  </si>
-  <si>
-    <t>Control de calidad corte LaserOT 4377</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Bodega ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1216774094398933</t>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46260.16929189815</v>
+        <v>46261.18440158565</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>155</v>
@@ -3856,8 +3856,8 @@
       <c r="R43" s="9">
         <v>46260</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>159</v>
+      <c r="S43" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -3868,17 +3868,17 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46260.169295162035</v>
+        <v>46261.18440128472</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -3911,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3919,8 +3919,8 @@
       <c r="R44" s="5">
         <v>46260</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>159</v>
+      <c r="S44" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -3931,17 +3931,17 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46225.00969839121</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46260.1692934375</v>
+        <v>46261.18440128472</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -3974,7 +3974,7 @@
         <v>108</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -3982,8 +3982,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>159</v>
+      <c r="S45" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -3994,17 +3994,17 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46254.16881054398</v>
+        <v>46261.1687259375</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4037,7 +4037,7 @@
         <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4046,7 +4046,7 @@
         <v>46261</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46254.16881052083</v>
+        <v>46261.168723229166</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>170</v>
@@ -4097,7 +4097,7 @@
         <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>171</v>
@@ -4109,7 +4109,7 @@
         <v>46261</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46254.168810902775</v>
+        <v>46261.168724953706</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -4160,10 +4160,10 @@
         <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4172,7 +4172,7 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>46262</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -542,43 +542,43 @@
     <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Bodega ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
+    <t>1216774094398933</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4377</t>
+  </si>
+  <si>
+    <t>Bodega ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094398961</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111396618</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales OT 4377,Control de calidad Armado OT 4377 ,Armado OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774205676924</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Caldereria,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774094398933</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4377</t>
-  </si>
-  <si>
-    <t>Bodega ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094398961</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111396618</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales OT 4377,Control de calidad Armado OT 4377 ,Armado OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774205676924</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Caldereria,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1216774245149624</t>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46225.009844733795</v>
+        <v>46262.51117300926</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46261.1687259375</v>
+        <v>46262.19512304398</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4045,8 +4045,8 @@
       <c r="R46" s="5">
         <v>46261</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>168</v>
+      <c r="S46" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4057,17 +4057,19 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="9">
         <v>46225.00971478009</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46262.511162361116</v>
+      </c>
       <c r="D47" s="9">
-        <v>46261.168723229166</v>
+        <v>46262.5111862037</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4100,7 +4102,7 @@
         <v>160</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4108,29 +4110,29 @@
       <c r="R47" s="9">
         <v>46261</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>168</v>
+      <c r="S47" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="11" t="s">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46261.168724953706</v>
+        <v>46262.19512244213</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4171,8 +4173,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>168</v>
+      <c r="S48" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4183,7 +4185,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46225.00973607639</v>
@@ -4193,7 +4195,7 @@
         <v>46225.00984827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4217,7 +4219,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4230,7 +4232,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4246,10 +4248,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4267,13 +4269,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4282,7 +4284,7 @@
         <v>46262</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4309,10 +4311,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4330,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>145</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4363,7 +4365,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46238.486620069445</v>
+        <v>46262.51117424769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>147</v>
@@ -4372,10 +4374,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4416,7 +4418,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46238.48661083334</v>
+        <v>46262.51117362268</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>147</v>
@@ -4425,10 +4427,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4499,13 +4501,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -6325,10 +6327,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I87" s="9">
         <v>46296</v>
@@ -6388,10 +6390,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6441,10 +6443,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I89" s="9">
         <v>46296</v>
@@ -6494,10 +6496,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I90" s="5">
         <v>46297</v>
@@ -6557,10 +6559,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="I91" s="9">
         <v>46297</v>
@@ -6610,10 +6612,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46259.17901423611</v>
+        <v>46266.16959359954</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>75</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46225.01480996527</v>
+        <v>46266.1923846412</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>182</v>
@@ -4346,8 +4346,8 @@
       <c r="R51" s="9">
         <v>46267</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>90</v>
+      <c r="S51" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -578,13 +578,13 @@
     <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Caldereria,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
+    <t>1216774245149624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT 4377 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774245149624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT 4377 </t>
   </si>
   <si>
     <t>1216774245149647</t>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46266.16959359954</v>
+        <v>46267.182458449075</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>75</v>
@@ -4283,8 +4283,8 @@
       <c r="R50" s="5">
         <v>46262</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>180</v>
+      <c r="S50" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B51" s="9">
         <v>46225.00974854166</v>
@@ -4305,7 +4305,7 @@
         <v>46266.1923846412</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4347,7 +4347,7 @@
         <v>46267</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>184</v>
@@ -4448,7 +4448,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>187</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46225.01496555556</v>
+        <v>46267.17804134259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -4515,8 +4515,8 @@
       <c r="R54" s="5">
         <v>46274</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>90</v>
+      <c r="S54" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46266.1923846412</v>
+        <v>46273.168694594904</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>181</v>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46262.51117424769</v>
+        <v>46273.16869640046</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>147</v>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46262.51117362268</v>
+        <v>46273.16869341435</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>147</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -584,28 +584,28 @@
     <t xml:space="preserve">Armado OT 4377 </t>
   </si>
   <si>
+    <t>1216774245149647</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Control de calidad Corte plasma OT 4377,Check Planos OT 4377,Preparacion materiales OT 4377</t>
+  </si>
+  <si>
+    <t>Armado OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774094425295</t>
+  </si>
+  <si>
+    <t>Check Planos OT 4377,Preparacion materiales OT 4377,Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Control de calidad Corte plasma OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225691696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4377 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774245149647</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Control de calidad Corte plasma OT 4377,Check Planos OT 4377,Preparacion materiales OT 4377</t>
-  </si>
-  <si>
-    <t>Armado OT 4377 ,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774094425295</t>
-  </si>
-  <si>
-    <t>Check Planos OT 4377,Preparacion materiales OT 4377,Control de calidad Mecanizado OT 4377,Control de calidad corte LaserOT 4377,Control de calidad Corte plasma OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225691696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4377 </t>
   </si>
   <si>
     <t>1216774225691719</t>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46273.168694594904</v>
+        <v>46274.14150798611</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>181</v>
@@ -4346,8 +4346,8 @@
       <c r="R51" s="9">
         <v>46267</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>182</v>
+      <c r="S51" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4398,10 +4398,10 @@
         <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="9">
         <v>46225.00976584491</v>
@@ -4451,10 +4451,10 @@
         <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4464,17 +4464,17 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46267.17804134259</v>
+        <v>46274.16861302083</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4516,7 +4516,7 @@
         <v>46274</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46238.48662065972</v>
+        <v>46274.16861446759</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>147</v>
@@ -4564,7 +4564,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>191</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46238.48661202546</v>
+        <v>46274.16861554398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>147</v>
@@ -4617,7 +4617,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>191</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46232.6243815625</v>
+        <v>46274.14918030093</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -4967,8 +4967,8 @@
       <c r="R62" s="5">
         <v>46275</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>90</v>
+      <c r="S62" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -605,70 +605,70 @@
     <t xml:space="preserve">Control de calidad Armado OT 4377 </t>
   </si>
   <si>
+    <t>1216774225691719</t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Check Planos OT 4377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Control de calidad Armado OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774225701067</t>
+  </si>
+  <si>
+    <t>1216774111464567</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete OT 4377,Recepcion motor OT 4377 ,Recepcion Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t>1216774245200834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4377 </t>
+  </si>
+  <si>
+    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Bodega:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774245200862</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774111474129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4377 </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+  </si>
+  <si>
+    <t>1216774225723410</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4377 ,Revestimiento OT 4377 ,Montaje motor OT 4377 ,Montaje Rodete OT 4377</t>
+  </si>
+  <si>
+    <t>1216774225731680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216774225691719</t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Check Planos OT 4377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Control de calidad Armado OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774225701067</t>
-  </si>
-  <si>
-    <t>1216774111464567</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete OT 4377,Recepcion motor OT 4377 ,Recepcion Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>1216774245200834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,Bodega:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774245200862</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>1216774111474129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4377 </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
-  </si>
-  <si>
-    <t>1216774225723410</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4377 ,Revestimiento OT 4377 ,Montaje motor OT 4377 ,Montaje Rodete OT 4377</t>
-  </si>
-  <si>
-    <t>1216774225731680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4377 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
   </si>
   <si>
     <t>1216774225731703</t>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46274.16861302083</v>
+        <v>46275.14099714121</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -4515,8 +4515,8 @@
       <c r="R54" s="5">
         <v>46274</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>189</v>
+      <c r="S54" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="9">
         <v>46225.00981328703</v>
@@ -4567,10 +4567,10 @@
         <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4620,10 +4620,10 @@
         <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46225.00990130787</v>
@@ -4643,7 +4643,7 @@
         <v>46225.010049375</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4667,7 +4667,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
@@ -4690,7 +4690,7 @@
         <v>46232.1720309375</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4717,13 +4717,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46225.00991375</v>
@@ -4753,7 +4753,7 @@
         <v>46232.172030752314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4780,13 +4780,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="9">
         <v>46231</v>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
@@ -4816,7 +4816,7 @@
         <v>46232.17203079861</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4843,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46225.009930162036</v>
@@ -4879,7 +4879,7 @@
         <v>46232.62468724537</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -4903,7 +4903,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46225.00993398148</v>
@@ -4926,7 +4926,7 @@
         <v>46274.14918030093</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q62" s="5">
         <v>46281</v>
@@ -4968,7 +4968,7 @@
         <v>46275</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>147</v>
@@ -5069,7 +5069,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>147</v>
@@ -5122,7 +5122,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>217</v>
@@ -5287,7 +5287,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>226</v>
@@ -5456,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q71" s="9">
         <v>46288</v>
@@ -5625,7 +5625,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>145</v>
@@ -5794,7 +5794,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>249</v>
